--- a/research/traditional_assets/database/data/qatar/qatar_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_oil_gas_production_and_exploration.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09378617660642248</v>
+        <v>0.09373289042981606</v>
       </c>
       <c r="C2">
-        <v>3351.968922856667</v>
+        <v>3323.008681338717</v>
       </c>
       <c r="D2">
-        <v>3135.568922856667</v>
+        <v>3139.054681338717</v>
       </c>
       <c r="E2">
-        <v>-1545.7</v>
+        <v>-1513.254</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32.44600000000001</v>
       </c>
       <c r="G2">
         <v>216.4</v>
@@ -1445,28 +1445,28 @@
         <v>245.675</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.6320338</v>
       </c>
       <c r="N2">
-        <v>245.675</v>
+        <v>244.0429662</v>
       </c>
       <c r="O2">
-        <v>24.5675</v>
+        <v>24.40429662</v>
       </c>
       <c r="P2">
-        <v>221.1075</v>
+        <v>219.63866958</v>
       </c>
       <c r="Q2">
-        <v>330.3074999999999</v>
+        <v>328.83866958</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09378617660642248</v>
+        <v>0.09422241457557178</v>
       </c>
       <c r="T2">
-        <v>0.9618186075065634</v>
+        <v>0.9705624130293503</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>150.5330343035787</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09373289042981606</v>
+        <v>0.09367960425320963</v>
       </c>
       <c r="C3">
-        <v>3323.008681338717</v>
+        <v>3294.056198562512</v>
       </c>
       <c r="D3">
-        <v>3139.054681338717</v>
+        <v>3142.548198562512</v>
       </c>
       <c r="E3">
-        <v>-1513.254</v>
+        <v>-1480.808</v>
       </c>
       <c r="F3">
-        <v>32.44600000000001</v>
+        <v>64.89200000000001</v>
       </c>
       <c r="G3">
         <v>216.4</v>
@@ -1527,28 +1527,28 @@
         <v>245.675</v>
       </c>
       <c r="M3">
-        <v>1.6320338</v>
+        <v>3.2640676</v>
       </c>
       <c r="N3">
-        <v>244.0429662</v>
+        <v>242.4109324</v>
       </c>
       <c r="O3">
-        <v>24.40429662</v>
+        <v>24.24109324</v>
       </c>
       <c r="P3">
-        <v>219.63866958</v>
+        <v>218.16983916</v>
       </c>
       <c r="Q3">
-        <v>328.83866958</v>
+        <v>327.36983916</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09422241457557178</v>
+        <v>0.094667555360418</v>
       </c>
       <c r="T3">
-        <v>0.9705624130293503</v>
+        <v>0.9794846635628065</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>150.5330343035787</v>
+        <v>75.26651715178936</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09367960425320963</v>
+        <v>0.09362631807660321</v>
       </c>
       <c r="C4">
-        <v>3294.056198562512</v>
+        <v>3265.111500461491</v>
       </c>
       <c r="D4">
-        <v>3142.548198562512</v>
+        <v>3146.049500461491</v>
       </c>
       <c r="E4">
-        <v>-1480.808</v>
+        <v>-1448.362</v>
       </c>
       <c r="F4">
-        <v>64.89200000000001</v>
+        <v>97.33800000000001</v>
       </c>
       <c r="G4">
         <v>216.4</v>
@@ -1609,28 +1609,28 @@
         <v>245.675</v>
       </c>
       <c r="M4">
-        <v>3.2640676</v>
+        <v>4.8961014</v>
       </c>
       <c r="N4">
-        <v>242.4109324</v>
+        <v>240.7788986</v>
       </c>
       <c r="O4">
-        <v>24.24109324</v>
+        <v>24.07788986</v>
       </c>
       <c r="P4">
-        <v>218.16983916</v>
+        <v>216.70100874</v>
       </c>
       <c r="Q4">
-        <v>327.36983916</v>
+        <v>325.90100874</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.094667555360418</v>
+        <v>0.09512187430577651</v>
       </c>
       <c r="T4">
-        <v>0.9794846635628065</v>
+        <v>0.9885908780247873</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>75.26651715178936</v>
+        <v>50.17767810119291</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09362631807660321</v>
+        <v>0.09357303189999679</v>
       </c>
       <c r="C5">
-        <v>3265.111500461491</v>
+        <v>3236.174613084802</v>
       </c>
       <c r="D5">
-        <v>3146.049500461491</v>
+        <v>3149.558613084802</v>
       </c>
       <c r="E5">
-        <v>-1448.362</v>
+        <v>-1415.916</v>
       </c>
       <c r="F5">
-        <v>97.33800000000001</v>
+        <v>129.784</v>
       </c>
       <c r="G5">
         <v>216.4</v>
@@ -1691,28 +1691,28 @@
         <v>245.675</v>
       </c>
       <c r="M5">
-        <v>4.8961014</v>
+        <v>6.5281352</v>
       </c>
       <c r="N5">
-        <v>240.7788986</v>
+        <v>239.1468647999999</v>
       </c>
       <c r="O5">
-        <v>24.07788986</v>
+        <v>23.91468648</v>
       </c>
       <c r="P5">
-        <v>216.70100874</v>
+        <v>215.2321783199999</v>
       </c>
       <c r="Q5">
-        <v>325.90100874</v>
+        <v>324.4321783199999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09512187430577651</v>
+        <v>0.09558565822916332</v>
       </c>
       <c r="T5">
-        <v>0.9885908780247873</v>
+        <v>0.9978868052880596</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>50.17767810119291</v>
+        <v>37.63325857589468</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09357303189999679</v>
+        <v>0.09351974572339036</v>
       </c>
       <c r="C6">
-        <v>3236.174613084802</v>
+        <v>3207.245562597944</v>
       </c>
       <c r="D6">
-        <v>3149.558613084802</v>
+        <v>3153.075562597944</v>
       </c>
       <c r="E6">
-        <v>-1415.916</v>
+        <v>-1383.47</v>
       </c>
       <c r="F6">
-        <v>129.784</v>
+        <v>162.23</v>
       </c>
       <c r="G6">
         <v>216.4</v>
@@ -1773,28 +1773,28 @@
         <v>245.675</v>
       </c>
       <c r="M6">
-        <v>6.5281352</v>
+        <v>8.160169</v>
       </c>
       <c r="N6">
-        <v>239.1468647999999</v>
+        <v>237.514831</v>
       </c>
       <c r="O6">
-        <v>23.91468648</v>
+        <v>23.7514831</v>
       </c>
       <c r="P6">
-        <v>215.2321783199999</v>
+        <v>213.7633479</v>
       </c>
       <c r="Q6">
-        <v>324.4321783199999</v>
+        <v>322.9633478999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09558565822916332</v>
+        <v>0.09605920602462144</v>
       </c>
       <c r="T6">
-        <v>0.9978868052880596</v>
+        <v>1.00737843628319</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>37.63325857589468</v>
+        <v>30.10660686071575</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09351974572339036</v>
+        <v>0.09346645954678395</v>
       </c>
       <c r="C7">
-        <v>3207.245562597944</v>
+        <v>3178.324375283414</v>
       </c>
       <c r="D7">
-        <v>3153.075562597944</v>
+        <v>3156.600375283414</v>
       </c>
       <c r="E7">
-        <v>-1383.47</v>
+        <v>-1351.024</v>
       </c>
       <c r="F7">
-        <v>162.23</v>
+        <v>194.676</v>
       </c>
       <c r="G7">
         <v>216.4</v>
@@ -1855,28 +1855,28 @@
         <v>245.675</v>
       </c>
       <c r="M7">
-        <v>8.160169</v>
+        <v>9.792202800000002</v>
       </c>
       <c r="N7">
-        <v>237.514831</v>
+        <v>235.8827971999999</v>
       </c>
       <c r="O7">
-        <v>23.7514831</v>
+        <v>23.58827972</v>
       </c>
       <c r="P7">
-        <v>213.7633479</v>
+        <v>212.2945174799999</v>
       </c>
       <c r="Q7">
-        <v>322.9633478999999</v>
+        <v>321.4945174799999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09605920602462144</v>
+        <v>0.09654282930508931</v>
       </c>
       <c r="T7">
-        <v>1.00737843628319</v>
+        <v>1.017072016873962</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.10660686071575</v>
+        <v>25.08883905059645</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09346645954678395</v>
+        <v>0.09341317337017752</v>
       </c>
       <c r="C8">
-        <v>3178.324375283414</v>
+        <v>3149.411077541371</v>
       </c>
       <c r="D8">
-        <v>3156.600375283414</v>
+        <v>3160.133077541371</v>
       </c>
       <c r="E8">
-        <v>-1351.024</v>
+        <v>-1318.578</v>
       </c>
       <c r="F8">
-        <v>194.676</v>
+        <v>227.122</v>
       </c>
       <c r="G8">
         <v>216.4</v>
@@ -1937,28 +1937,28 @@
         <v>245.675</v>
       </c>
       <c r="M8">
-        <v>9.7922028</v>
+        <v>11.4242366</v>
       </c>
       <c r="N8">
-        <v>235.8827971999999</v>
+        <v>234.2507634</v>
       </c>
       <c r="O8">
-        <v>23.58827972</v>
+        <v>23.42507634</v>
       </c>
       <c r="P8">
-        <v>212.2945174799999</v>
+        <v>210.82568706</v>
       </c>
       <c r="Q8">
-        <v>321.4945174799999</v>
+        <v>320.0256870599999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09654282930508931</v>
+        <v>0.09703685308621238</v>
       </c>
       <c r="T8">
-        <v>1.017072016873962</v>
+        <v>1.026974061563459</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.08883905059646</v>
+        <v>21.50471918622553</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09341317337017752</v>
+        <v>0.09335988719357111</v>
       </c>
       <c r="C9">
-        <v>3149.411077541371</v>
+        <v>3120.50569589028</v>
       </c>
       <c r="D9">
-        <v>3160.133077541371</v>
+        <v>3163.67369589028</v>
       </c>
       <c r="E9">
-        <v>-1318.578</v>
+        <v>-1286.132</v>
       </c>
       <c r="F9">
-        <v>227.122</v>
+        <v>259.568</v>
       </c>
       <c r="G9">
         <v>216.4</v>
@@ -2019,28 +2019,28 @@
         <v>245.675</v>
       </c>
       <c r="M9">
-        <v>11.4242366</v>
+        <v>13.0562704</v>
       </c>
       <c r="N9">
-        <v>234.2507634</v>
+        <v>232.6187296</v>
       </c>
       <c r="O9">
-        <v>23.42507634</v>
+        <v>23.26187296</v>
       </c>
       <c r="P9">
-        <v>210.82568706</v>
+        <v>209.35685664</v>
       </c>
       <c r="Q9">
-        <v>320.0256870599999</v>
+        <v>318.55685664</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09703685308621239</v>
+        <v>0.0975416165147512</v>
       </c>
       <c r="T9">
-        <v>1.02697406156346</v>
+        <v>1.037091368094034</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.50471918622553</v>
+        <v>18.81662928794734</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09335988719357111</v>
+        <v>0.09330660101696468</v>
       </c>
       <c r="C10">
-        <v>3120.50569589028</v>
+        <v>3091.608256967594</v>
       </c>
       <c r="D10">
-        <v>3163.67369589028</v>
+        <v>3167.222256967594</v>
       </c>
       <c r="E10">
-        <v>-1286.132</v>
+        <v>-1253.686</v>
       </c>
       <c r="F10">
-        <v>259.568</v>
+        <v>292.014</v>
       </c>
       <c r="G10">
         <v>216.4</v>
@@ -2101,28 +2101,28 @@
         <v>245.675</v>
       </c>
       <c r="M10">
-        <v>13.0562704</v>
+        <v>14.6883042</v>
       </c>
       <c r="N10">
-        <v>232.6187296</v>
+        <v>230.9866957999999</v>
       </c>
       <c r="O10">
-        <v>23.26187296</v>
+        <v>23.09866958</v>
       </c>
       <c r="P10">
-        <v>209.35685664</v>
+        <v>207.8880262199999</v>
       </c>
       <c r="Q10">
-        <v>318.55685664</v>
+        <v>317.08802622</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0975416165147512</v>
+        <v>0.09805747364501613</v>
       </c>
       <c r="T10">
-        <v>1.037091368094034</v>
+        <v>1.047431033009895</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.81662928794734</v>
+        <v>16.72589270039764</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09330660101696468</v>
+        <v>0.09325331484035827</v>
       </c>
       <c r="C11">
-        <v>3091.608256967594</v>
+        <v>3062.718787530408</v>
       </c>
       <c r="D11">
-        <v>3167.222256967594</v>
+        <v>3170.778787530407</v>
       </c>
       <c r="E11">
-        <v>-1253.686</v>
+        <v>-1221.24</v>
       </c>
       <c r="F11">
-        <v>292.014</v>
+        <v>324.46</v>
       </c>
       <c r="G11">
         <v>216.4</v>
@@ -2183,28 +2183,28 @@
         <v>245.675</v>
       </c>
       <c r="M11">
-        <v>14.6883042</v>
+        <v>16.320338</v>
       </c>
       <c r="N11">
-        <v>230.9866957999999</v>
+        <v>229.354662</v>
       </c>
       <c r="O11">
-        <v>23.09866958</v>
+        <v>22.9354662</v>
       </c>
       <c r="P11">
-        <v>207.8880262199999</v>
+        <v>206.4191958</v>
       </c>
       <c r="Q11">
-        <v>317.08802622</v>
+        <v>315.6191957999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09805747364501613</v>
+        <v>0.09858479426706473</v>
       </c>
       <c r="T11">
-        <v>1.047431033009895</v>
+        <v>1.05800046825722</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.72589270039764</v>
+        <v>15.05330343035787</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09325331484035827</v>
+        <v>0.09320002866375185</v>
       </c>
       <c r="C12">
-        <v>3062.718787530408</v>
+        <v>3033.837314456136</v>
       </c>
       <c r="D12">
-        <v>3170.778787530407</v>
+        <v>3174.343314456136</v>
       </c>
       <c r="E12">
-        <v>-1221.24</v>
+        <v>-1188.794</v>
       </c>
       <c r="F12">
-        <v>324.46</v>
+        <v>356.9060000000001</v>
       </c>
       <c r="G12">
         <v>216.4</v>
@@ -2265,28 +2265,28 @@
         <v>245.675</v>
       </c>
       <c r="M12">
-        <v>16.320338</v>
+        <v>17.9523718</v>
       </c>
       <c r="N12">
-        <v>229.354662</v>
+        <v>227.7226281999999</v>
       </c>
       <c r="O12">
-        <v>22.9354662</v>
+        <v>22.77226281999999</v>
       </c>
       <c r="P12">
-        <v>206.4191958</v>
+        <v>204.9503653799999</v>
       </c>
       <c r="Q12">
-        <v>315.6191957999999</v>
+        <v>314.1503653799999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09858479426706473</v>
+        <v>0.09912396479073241</v>
       </c>
       <c r="T12">
-        <v>1.05800046825722</v>
+        <v>1.068807418903361</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.05330343035787</v>
+        <v>13.68482130032534</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09320002866375185</v>
+        <v>0.09330874248714542</v>
       </c>
       <c r="C13">
-        <v>3033.837314456136</v>
+        <v>2994.127493516828</v>
       </c>
       <c r="D13">
-        <v>3174.343314456136</v>
+        <v>3167.079493516827</v>
       </c>
       <c r="E13">
-        <v>-1188.794</v>
+        <v>-1156.348</v>
       </c>
       <c r="F13">
-        <v>356.9060000000001</v>
+        <v>389.352</v>
       </c>
       <c r="G13">
         <v>216.4</v>
@@ -2347,45 +2347,45 @@
         <v>245.675</v>
       </c>
       <c r="M13">
-        <v>17.9523718</v>
+        <v>20.1684336</v>
       </c>
       <c r="N13">
-        <v>227.7226281999999</v>
+        <v>225.5065663999999</v>
       </c>
       <c r="O13">
-        <v>22.77226281999999</v>
+        <v>22.55065664</v>
       </c>
       <c r="P13">
-        <v>204.9503653799999</v>
+        <v>202.9559097599999</v>
       </c>
       <c r="Q13">
-        <v>314.1503653799999</v>
+        <v>312.1559097599999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09912396479073241</v>
+        <v>0.09967538918993797</v>
       </c>
       <c r="T13">
-        <v>1.068807418903361</v>
+        <v>1.079859982064187</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.1</v>
       </c>
       <c r="W13">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.68482130032534</v>
+        <v>12.18116413363901</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09330874248714542</v>
+        <v>0.09326895631053898</v>
       </c>
       <c r="C14">
-        <v>2994.127493516828</v>
+        <v>2964.335985923009</v>
       </c>
       <c r="D14">
-        <v>3167.079493516827</v>
+        <v>3169.733985923009</v>
       </c>
       <c r="E14">
-        <v>-1156.348</v>
+        <v>-1123.902</v>
       </c>
       <c r="F14">
-        <v>389.352</v>
+        <v>421.7980000000001</v>
       </c>
       <c r="G14">
         <v>216.4</v>
@@ -2429,28 +2429,28 @@
         <v>245.675</v>
       </c>
       <c r="M14">
-        <v>20.1684336</v>
+        <v>21.8491364</v>
       </c>
       <c r="N14">
-        <v>225.5065663999999</v>
+        <v>223.8258636</v>
       </c>
       <c r="O14">
-        <v>22.55065664</v>
+        <v>22.38258636</v>
       </c>
       <c r="P14">
-        <v>202.9559097599999</v>
+        <v>201.44327724</v>
       </c>
       <c r="Q14">
-        <v>312.1559097599999</v>
+        <v>310.64327724</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09967538918993797</v>
+        <v>0.1002394900121138</v>
       </c>
       <c r="T14">
-        <v>1.079859982064187</v>
+        <v>1.091166627136756</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.18116413363901</v>
+        <v>11.24415150797447</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09326895631053898</v>
+        <v>0.09322917013393256</v>
       </c>
       <c r="C15">
-        <v>2964.335985923009</v>
+        <v>2934.548931795417</v>
       </c>
       <c r="D15">
-        <v>3169.733985923009</v>
+        <v>3172.392931795417</v>
       </c>
       <c r="E15">
-        <v>-1123.902</v>
+        <v>-1091.456</v>
       </c>
       <c r="F15">
-        <v>421.7980000000001</v>
+        <v>454.2440000000001</v>
       </c>
       <c r="G15">
         <v>216.4</v>
@@ -2511,28 +2511,28 @@
         <v>245.675</v>
       </c>
       <c r="M15">
-        <v>21.8491364</v>
+        <v>23.5298392</v>
       </c>
       <c r="N15">
-        <v>223.8258636</v>
+        <v>222.1451608</v>
       </c>
       <c r="O15">
-        <v>22.38258636</v>
+        <v>22.21451608</v>
       </c>
       <c r="P15">
-        <v>201.44327724</v>
+        <v>199.93064472</v>
       </c>
       <c r="Q15">
-        <v>310.64327724</v>
+        <v>309.13064472</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1002394900121138</v>
+        <v>0.1008167094580611</v>
       </c>
       <c r="T15">
-        <v>1.091166627136756</v>
+        <v>1.102736217443572</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.24415150797447</v>
+        <v>10.44099782883344</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09322917013393256</v>
+        <v>0.09341888395732616</v>
       </c>
       <c r="C16">
-        <v>2934.548931795417</v>
+        <v>2889.464105716731</v>
       </c>
       <c r="D16">
-        <v>3172.392931795417</v>
+        <v>3159.754105716731</v>
       </c>
       <c r="E16">
-        <v>-1091.456</v>
+        <v>-1059.01</v>
       </c>
       <c r="F16">
-        <v>454.2440000000001</v>
+        <v>486.6900000000001</v>
       </c>
       <c r="G16">
         <v>216.4</v>
@@ -2593,45 +2593,45 @@
         <v>245.675</v>
       </c>
       <c r="M16">
-        <v>23.5298392</v>
+        <v>26.03791500000001</v>
       </c>
       <c r="N16">
-        <v>222.1451608</v>
+        <v>219.637085</v>
       </c>
       <c r="O16">
-        <v>22.21451608</v>
+        <v>21.9637085</v>
       </c>
       <c r="P16">
-        <v>199.93064472</v>
+        <v>197.6733765</v>
       </c>
       <c r="Q16">
-        <v>309.13064472</v>
+        <v>306.8733764999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1008167094580611</v>
+        <v>0.1014075105380308</v>
       </c>
       <c r="T16">
-        <v>1.102736217443572</v>
+        <v>1.114578033404665</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.1</v>
       </c>
       <c r="W16">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.44099782883344</v>
+        <v>9.435279284074777</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09341888395732614</v>
+        <v>0.09339439778071973</v>
       </c>
       <c r="C17">
-        <v>2889.464105716732</v>
+        <v>2858.643723450607</v>
       </c>
       <c r="D17">
-        <v>3159.754105716732</v>
+        <v>3161.379723450606</v>
       </c>
       <c r="E17">
-        <v>-1059.01</v>
+        <v>-1026.564</v>
       </c>
       <c r="F17">
-        <v>486.6900000000001</v>
+        <v>519.1360000000001</v>
       </c>
       <c r="G17">
         <v>216.4</v>
@@ -2675,28 +2675,28 @@
         <v>245.675</v>
       </c>
       <c r="M17">
-        <v>26.037915</v>
+        <v>27.77377600000001</v>
       </c>
       <c r="N17">
-        <v>219.637085</v>
+        <v>217.901224</v>
       </c>
       <c r="O17">
-        <v>21.9637085</v>
+        <v>21.7901224</v>
       </c>
       <c r="P17">
-        <v>197.6733765</v>
+        <v>196.1111016</v>
       </c>
       <c r="Q17">
-        <v>306.8733764999999</v>
+        <v>305.3111015999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1014075105380308</v>
+        <v>0.1020123783103806</v>
       </c>
       <c r="T17">
-        <v>1.114578033404665</v>
+        <v>1.126701797364831</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.435279284074779</v>
+        <v>8.845574328820105</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09339439778071973</v>
+        <v>0.0933699116041133</v>
       </c>
       <c r="C18">
-        <v>2858.643723450607</v>
+        <v>2827.825014728181</v>
       </c>
       <c r="D18">
-        <v>3161.379723450606</v>
+        <v>3163.007014728182</v>
       </c>
       <c r="E18">
-        <v>-1026.564</v>
+        <v>-994.1179999999999</v>
       </c>
       <c r="F18">
-        <v>519.1360000000001</v>
+        <v>551.5820000000001</v>
       </c>
       <c r="G18">
         <v>216.4</v>
@@ -2757,28 +2757,28 @@
         <v>245.675</v>
       </c>
       <c r="M18">
-        <v>27.77377600000001</v>
+        <v>29.50963700000001</v>
       </c>
       <c r="N18">
-        <v>217.901224</v>
+        <v>216.165363</v>
       </c>
       <c r="O18">
-        <v>21.7901224</v>
+        <v>21.6165363</v>
       </c>
       <c r="P18">
-        <v>196.1111016</v>
+        <v>194.5488266999999</v>
       </c>
       <c r="Q18">
-        <v>305.3111015999999</v>
+        <v>303.7488266999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1020123783103806</v>
+        <v>0.1026318212097751</v>
       </c>
       <c r="T18">
-        <v>1.126701797364831</v>
+        <v>1.139117700215605</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.845574328820105</v>
+        <v>8.325246427124803</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0933699116041133</v>
+        <v>0.09334542542750687</v>
       </c>
       <c r="C19">
-        <v>2827.825014728181</v>
+        <v>2797.007982135111</v>
       </c>
       <c r="D19">
-        <v>3163.007014728182</v>
+        <v>3164.635982135112</v>
       </c>
       <c r="E19">
-        <v>-994.1179999999999</v>
+        <v>-961.6719999999999</v>
       </c>
       <c r="F19">
-        <v>551.5820000000001</v>
+        <v>584.0280000000001</v>
       </c>
       <c r="G19">
         <v>216.4</v>
@@ -2839,28 +2839,28 @@
         <v>245.675</v>
       </c>
       <c r="M19">
-        <v>29.50963700000001</v>
+        <v>31.245498</v>
       </c>
       <c r="N19">
-        <v>216.165363</v>
+        <v>214.429502</v>
       </c>
       <c r="O19">
-        <v>21.6165363</v>
+        <v>21.4429502</v>
       </c>
       <c r="P19">
-        <v>194.5488266999999</v>
+        <v>192.9865518</v>
       </c>
       <c r="Q19">
-        <v>303.7488266999999</v>
+        <v>302.1865518</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1026318212097751</v>
+        <v>0.1032663724725694</v>
       </c>
       <c r="T19">
-        <v>1.139117700215605</v>
+        <v>1.151836429965177</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.325246427124803</v>
+        <v>7.862732736728982</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09334542542750687</v>
+        <v>0.09345773925090045</v>
       </c>
       <c r="C20">
-        <v>2797.007982135112</v>
+        <v>2757.10396225441</v>
       </c>
       <c r="D20">
-        <v>3164.635982135112</v>
+        <v>3157.17796225441</v>
       </c>
       <c r="E20">
-        <v>-961.672</v>
+        <v>-929.226</v>
       </c>
       <c r="F20">
-        <v>584.028</v>
+        <v>616.474</v>
       </c>
       <c r="G20">
         <v>216.4</v>
@@ -2921,45 +2921,45 @@
         <v>245.675</v>
       </c>
       <c r="M20">
-        <v>31.245498</v>
+        <v>33.4745382</v>
       </c>
       <c r="N20">
-        <v>214.429502</v>
+        <v>212.2004617999999</v>
       </c>
       <c r="O20">
-        <v>21.4429502</v>
+        <v>21.22004618</v>
       </c>
       <c r="P20">
-        <v>192.9865518</v>
+        <v>190.9804156199999</v>
       </c>
       <c r="Q20">
-        <v>302.1865518</v>
+        <v>300.18041562</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1032663724725694</v>
+        <v>0.1039165916677783</v>
       </c>
       <c r="T20">
-        <v>1.151836429965177</v>
+        <v>1.164869202424616</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.1</v>
       </c>
       <c r="W20">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.862732736728982</v>
+        <v>7.339160245681893</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09345773925090045</v>
+        <v>0.09344045307429405</v>
       </c>
       <c r="C21">
-        <v>2757.10396225441</v>
+        <v>2725.803533555931</v>
       </c>
       <c r="D21">
-        <v>3157.17796225441</v>
+        <v>3158.323533555931</v>
       </c>
       <c r="E21">
-        <v>-929.226</v>
+        <v>-896.78</v>
       </c>
       <c r="F21">
-        <v>616.474</v>
+        <v>648.9200000000001</v>
       </c>
       <c r="G21">
         <v>216.4</v>
@@ -3003,28 +3003,28 @@
         <v>245.675</v>
       </c>
       <c r="M21">
-        <v>33.4745382</v>
+        <v>35.23635600000001</v>
       </c>
       <c r="N21">
-        <v>212.2004617999999</v>
+        <v>210.438644</v>
       </c>
       <c r="O21">
-        <v>21.22004618</v>
+        <v>21.0438644</v>
       </c>
       <c r="P21">
-        <v>190.9804156199999</v>
+        <v>189.3947796</v>
       </c>
       <c r="Q21">
-        <v>300.18041562</v>
+        <v>298.5947795999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1039165916677783</v>
+        <v>0.1045830663428675</v>
       </c>
       <c r="T21">
-        <v>1.164869202424616</v>
+        <v>1.17822779419554</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.339160245681893</v>
+        <v>6.972202233397798</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09344045307429405</v>
+        <v>0.09342316689768761</v>
       </c>
       <c r="C22">
-        <v>2725.803533555931</v>
+        <v>2694.503936492524</v>
       </c>
       <c r="D22">
-        <v>3158.323533555931</v>
+        <v>3159.469936492524</v>
       </c>
       <c r="E22">
-        <v>-896.78</v>
+        <v>-864.3339999999999</v>
       </c>
       <c r="F22">
-        <v>648.9200000000001</v>
+        <v>681.3660000000001</v>
       </c>
       <c r="G22">
         <v>216.4</v>
@@ -3085,28 +3085,28 @@
         <v>245.675</v>
       </c>
       <c r="M22">
-        <v>35.23635600000001</v>
+        <v>36.9981738</v>
       </c>
       <c r="N22">
-        <v>210.438644</v>
+        <v>208.6768261999999</v>
       </c>
       <c r="O22">
-        <v>21.0438644</v>
+        <v>20.86768262</v>
       </c>
       <c r="P22">
-        <v>189.3947796</v>
+        <v>187.80914358</v>
       </c>
       <c r="Q22">
-        <v>298.5947795999999</v>
+        <v>297.0091435799999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1045830663428675</v>
+        <v>0.1052664137945413</v>
       </c>
       <c r="T22">
-        <v>1.17822779419554</v>
+        <v>1.191924578163197</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.972202233397798</v>
+        <v>6.640192603235999</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09342316689768761</v>
+        <v>0.09340588072108119</v>
       </c>
       <c r="C23">
-        <v>2694.503936492524</v>
+        <v>2663.205171970108</v>
       </c>
       <c r="D23">
-        <v>3159.469936492524</v>
+        <v>3160.617171970107</v>
       </c>
       <c r="E23">
-        <v>-864.3339999999999</v>
+        <v>-831.8879999999999</v>
       </c>
       <c r="F23">
-        <v>681.3660000000001</v>
+        <v>713.8120000000001</v>
       </c>
       <c r="G23">
         <v>216.4</v>
@@ -3167,28 +3167,28 @@
         <v>245.675</v>
       </c>
       <c r="M23">
-        <v>36.9981738</v>
+        <v>38.75999160000001</v>
       </c>
       <c r="N23">
-        <v>208.6768261999999</v>
+        <v>206.9150083999999</v>
       </c>
       <c r="O23">
-        <v>20.86768262</v>
+        <v>20.69150084</v>
       </c>
       <c r="P23">
-        <v>187.80914358</v>
+        <v>186.2235075599999</v>
       </c>
       <c r="Q23">
-        <v>297.0091435799999</v>
+        <v>295.42350756</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1052664137945413</v>
+        <v>0.1059672829757451</v>
       </c>
       <c r="T23">
-        <v>1.191924578163197</v>
+        <v>1.205972561719768</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.640192603235999</v>
+        <v>6.338365666725271</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09340588072108119</v>
+        <v>0.09359559454447478</v>
       </c>
       <c r="C24">
-        <v>2663.205171970108</v>
+        <v>2618.213815568695</v>
       </c>
       <c r="D24">
-        <v>3160.617171970107</v>
+        <v>3148.071815568695</v>
       </c>
       <c r="E24">
-        <v>-831.8879999999999</v>
+        <v>-799.4419999999999</v>
       </c>
       <c r="F24">
-        <v>713.8120000000001</v>
+        <v>746.2580000000002</v>
       </c>
       <c r="G24">
         <v>216.4</v>
@@ -3249,45 +3249,45 @@
         <v>245.675</v>
       </c>
       <c r="M24">
-        <v>38.75999160000001</v>
+        <v>41.26806740000001</v>
       </c>
       <c r="N24">
-        <v>206.9150083999999</v>
+        <v>204.4069325999999</v>
       </c>
       <c r="O24">
-        <v>20.69150084</v>
+        <v>20.44069326</v>
       </c>
       <c r="P24">
-        <v>186.2235075599999</v>
+        <v>183.96623934</v>
       </c>
       <c r="Q24">
-        <v>295.42350756</v>
+        <v>293.1662393399999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1059672829757451</v>
+        <v>0.1066863565512659</v>
       </c>
       <c r="T24">
-        <v>1.205972561719768</v>
+        <v>1.22038542796612</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.1</v>
       </c>
       <c r="W24">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.338365666725271</v>
+        <v>5.953150110441079</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09359559454447478</v>
+        <v>0.09358730836786835</v>
       </c>
       <c r="C25">
-        <v>2618.213815568695</v>
+        <v>2586.313681823238</v>
       </c>
       <c r="D25">
-        <v>3148.071815568695</v>
+        <v>3148.617681823238</v>
       </c>
       <c r="E25">
-        <v>-799.4419999999999</v>
+        <v>-766.9959999999999</v>
       </c>
       <c r="F25">
-        <v>746.2580000000002</v>
+        <v>778.7040000000002</v>
       </c>
       <c r="G25">
         <v>216.4</v>
@@ -3331,28 +3331,28 @@
         <v>245.675</v>
       </c>
       <c r="M25">
-        <v>41.26806740000001</v>
+        <v>43.06233120000001</v>
       </c>
       <c r="N25">
-        <v>204.4069325999999</v>
+        <v>202.6126687999999</v>
       </c>
       <c r="O25">
-        <v>20.44069326</v>
+        <v>20.26126687999999</v>
       </c>
       <c r="P25">
-        <v>183.96623934</v>
+        <v>182.3514019199999</v>
       </c>
       <c r="Q25">
-        <v>293.1662393399999</v>
+        <v>291.5514019199999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1066863565512659</v>
+        <v>0.1074243531156162</v>
       </c>
       <c r="T25">
-        <v>1.22038542796612</v>
+        <v>1.235177580166324</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.953150110441079</v>
+        <v>5.705102189172701</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09358730836786835</v>
+        <v>0.09357902219126191</v>
       </c>
       <c r="C26">
-        <v>2586.313681823238</v>
+        <v>2554.413737413772</v>
       </c>
       <c r="D26">
-        <v>3148.617681823238</v>
+        <v>3149.163737413772</v>
       </c>
       <c r="E26">
-        <v>-766.996</v>
+        <v>-734.55</v>
       </c>
       <c r="F26">
-        <v>778.7040000000001</v>
+        <v>811.1500000000001</v>
       </c>
       <c r="G26">
         <v>216.4</v>
@@ -3413,28 +3413,28 @@
         <v>245.675</v>
       </c>
       <c r="M26">
-        <v>43.0623312</v>
+        <v>44.85659500000001</v>
       </c>
       <c r="N26">
-        <v>202.6126687999999</v>
+        <v>200.818405</v>
       </c>
       <c r="O26">
-        <v>20.26126687999999</v>
+        <v>20.0818405</v>
       </c>
       <c r="P26">
-        <v>182.3514019199999</v>
+        <v>180.7365645</v>
       </c>
       <c r="Q26">
-        <v>291.5514019199999</v>
+        <v>289.9365644999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1074243531156162</v>
+        <v>0.1081820295883492</v>
       </c>
       <c r="T26">
-        <v>1.235177580166324</v>
+        <v>1.250364189758532</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.705102189172702</v>
+        <v>5.476898101605793</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09357902219126191</v>
+        <v>0.0935707360146555</v>
       </c>
       <c r="C27">
-        <v>2554.413737413772</v>
+        <v>2522.513982438817</v>
       </c>
       <c r="D27">
-        <v>3149.163737413772</v>
+        <v>3149.709982438816</v>
       </c>
       <c r="E27">
-        <v>-734.55</v>
+        <v>-702.1039999999999</v>
       </c>
       <c r="F27">
-        <v>811.1500000000001</v>
+        <v>843.5960000000001</v>
       </c>
       <c r="G27">
         <v>216.4</v>
@@ -3495,28 +3495,28 @@
         <v>245.675</v>
       </c>
       <c r="M27">
-        <v>44.85659500000001</v>
+        <v>46.65085880000001</v>
       </c>
       <c r="N27">
-        <v>200.818405</v>
+        <v>199.0241411999999</v>
       </c>
       <c r="O27">
-        <v>20.0818405</v>
+        <v>19.90241412</v>
       </c>
       <c r="P27">
-        <v>180.7365645</v>
+        <v>179.1217270799999</v>
       </c>
       <c r="Q27">
-        <v>289.9365644999999</v>
+        <v>288.32172708</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1081820295883492</v>
+        <v>0.1089601838035885</v>
       </c>
       <c r="T27">
-        <v>1.250364189758532</v>
+        <v>1.265961248258639</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.476898101605793</v>
+        <v>5.266248174620955</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0935707360146555</v>
+        <v>0.09356244983804908</v>
       </c>
       <c r="C28">
-        <v>2522.513982438817</v>
+        <v>2490.614416996968</v>
       </c>
       <c r="D28">
-        <v>3149.709982438816</v>
+        <v>3150.256416996968</v>
       </c>
       <c r="E28">
-        <v>-702.1039999999999</v>
+        <v>-669.6579999999999</v>
       </c>
       <c r="F28">
-        <v>843.5960000000001</v>
+        <v>876.0420000000001</v>
       </c>
       <c r="G28">
         <v>216.4</v>
@@ -3577,28 +3577,28 @@
         <v>245.675</v>
       </c>
       <c r="M28">
-        <v>46.65085880000001</v>
+        <v>48.44512260000001</v>
       </c>
       <c r="N28">
-        <v>199.0241411999999</v>
+        <v>197.2298773999999</v>
       </c>
       <c r="O28">
-        <v>19.90241412</v>
+        <v>19.72298773999999</v>
       </c>
       <c r="P28">
-        <v>179.1217270799999</v>
+        <v>177.50688966</v>
       </c>
       <c r="Q28">
-        <v>288.32172708</v>
+        <v>286.7068896599999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1089601838035885</v>
+        <v>0.109759657312396</v>
       </c>
       <c r="T28">
-        <v>1.265961248258639</v>
+        <v>1.281985623429981</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.266248174620955</v>
+        <v>5.071201945931289</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09356244983804908</v>
+        <v>0.09355416366144266</v>
       </c>
       <c r="C29">
-        <v>2490.614416996968</v>
+        <v>2458.715041186888</v>
       </c>
       <c r="D29">
-        <v>3150.256416996968</v>
+        <v>3150.803041186888</v>
       </c>
       <c r="E29">
-        <v>-669.6579999999999</v>
+        <v>-637.2119999999999</v>
       </c>
       <c r="F29">
-        <v>876.0420000000001</v>
+        <v>908.4880000000002</v>
       </c>
       <c r="G29">
         <v>216.4</v>
@@ -3659,28 +3659,28 @@
         <v>245.675</v>
       </c>
       <c r="M29">
-        <v>48.44512260000001</v>
+        <v>50.23938640000001</v>
       </c>
       <c r="N29">
-        <v>197.2298773999999</v>
+        <v>195.4356136</v>
       </c>
       <c r="O29">
-        <v>19.72298773999999</v>
+        <v>19.54356136</v>
       </c>
       <c r="P29">
-        <v>177.50688966</v>
+        <v>175.8920522399999</v>
       </c>
       <c r="Q29">
-        <v>286.7068896599999</v>
+        <v>285.0920522399999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.109759657312396</v>
+        <v>0.1105813384186703</v>
       </c>
       <c r="T29">
-        <v>1.281985623429981</v>
+        <v>1.298455120133861</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.071201945931289</v>
+        <v>4.890087590719459</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09355416366144266</v>
+        <v>0.09354587748483623</v>
       </c>
       <c r="C30">
-        <v>2458.715041186888</v>
+        <v>2426.815855107307</v>
       </c>
       <c r="D30">
-        <v>3150.803041186888</v>
+        <v>3151.349855107308</v>
       </c>
       <c r="E30">
-        <v>-637.2119999999999</v>
+        <v>-604.7659999999998</v>
       </c>
       <c r="F30">
-        <v>908.4880000000002</v>
+        <v>940.9340000000002</v>
       </c>
       <c r="G30">
         <v>216.4</v>
@@ -3741,28 +3741,28 @@
         <v>245.675</v>
       </c>
       <c r="M30">
-        <v>50.23938640000001</v>
+        <v>52.03365020000001</v>
       </c>
       <c r="N30">
-        <v>195.4356136</v>
+        <v>193.6413497999999</v>
       </c>
       <c r="O30">
-        <v>19.54356136</v>
+        <v>19.36413498</v>
       </c>
       <c r="P30">
-        <v>175.8920522399999</v>
+        <v>174.27721482</v>
       </c>
       <c r="Q30">
-        <v>285.0920522399999</v>
+        <v>283.47721482</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1105813384186703</v>
+        <v>0.1114261654716003</v>
       </c>
       <c r="T30">
-        <v>1.298455120133861</v>
+        <v>1.315388546322357</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.890087590719459</v>
+        <v>4.72146388069465</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09354587748483623</v>
+        <v>0.09353759130822981</v>
       </c>
       <c r="C31">
-        <v>2426.815855107307</v>
+        <v>2394.916858857024</v>
       </c>
       <c r="D31">
-        <v>3151.349855107308</v>
+        <v>3151.896858857024</v>
       </c>
       <c r="E31">
-        <v>-604.766</v>
+        <v>-572.3199999999999</v>
       </c>
       <c r="F31">
-        <v>940.9340000000001</v>
+        <v>973.3800000000001</v>
       </c>
       <c r="G31">
         <v>216.4</v>
@@ -3823,28 +3823,28 @@
         <v>245.675</v>
       </c>
       <c r="M31">
-        <v>52.0336502</v>
+        <v>53.82791400000001</v>
       </c>
       <c r="N31">
-        <v>193.6413497999999</v>
+        <v>191.8470859999999</v>
       </c>
       <c r="O31">
-        <v>19.36413498</v>
+        <v>19.18470859999999</v>
       </c>
       <c r="P31">
-        <v>174.27721482</v>
+        <v>172.6623773999999</v>
       </c>
       <c r="Q31">
-        <v>283.47721482</v>
+        <v>281.8623773999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1114261654716003</v>
+        <v>0.1122951304403283</v>
       </c>
       <c r="T31">
-        <v>1.315388546322356</v>
+        <v>1.332805784687666</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.72146388069465</v>
+        <v>4.564081751338161</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09353759130822981</v>
+        <v>0.0942268051316234</v>
       </c>
       <c r="C32">
-        <v>2394.916858857024</v>
+        <v>2317.612832829274</v>
       </c>
       <c r="D32">
-        <v>3151.896858857024</v>
+        <v>3107.038832829274</v>
       </c>
       <c r="E32">
-        <v>-572.3199999999999</v>
+        <v>-539.8739999999999</v>
       </c>
       <c r="F32">
-        <v>973.3800000000001</v>
+        <v>1005.826</v>
       </c>
       <c r="G32">
         <v>216.4</v>
@@ -3905,45 +3905,45 @@
         <v>245.675</v>
       </c>
       <c r="M32">
-        <v>53.82791400000001</v>
+        <v>58.13674280000001</v>
       </c>
       <c r="N32">
-        <v>191.8470859999999</v>
+        <v>187.5382571999999</v>
       </c>
       <c r="O32">
-        <v>19.18470859999999</v>
+        <v>18.75382571999999</v>
       </c>
       <c r="P32">
-        <v>172.6623773999999</v>
+        <v>168.78443148</v>
       </c>
       <c r="Q32">
-        <v>281.8623773999999</v>
+        <v>277.98443148</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1122951304403283</v>
+        <v>0.1131892827994542</v>
       </c>
       <c r="T32">
-        <v>1.332805784687666</v>
+        <v>1.350727870541826</v>
       </c>
       <c r="U32">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.1</v>
       </c>
       <c r="W32">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.564081751338161</v>
+        <v>4.225812939764488</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0942268051316234</v>
+        <v>0.09424101895501695</v>
       </c>
       <c r="C33">
-        <v>2317.612832829274</v>
+        <v>2284.255148843276</v>
       </c>
       <c r="D33">
-        <v>3107.038832829274</v>
+        <v>3106.127148843276</v>
       </c>
       <c r="E33">
-        <v>-539.8739999999999</v>
+        <v>-507.4279999999999</v>
       </c>
       <c r="F33">
-        <v>1005.826</v>
+        <v>1038.272</v>
       </c>
       <c r="G33">
         <v>216.4</v>
@@ -3987,28 +3987,28 @@
         <v>245.675</v>
       </c>
       <c r="M33">
-        <v>58.13674280000001</v>
+        <v>60.01212160000001</v>
       </c>
       <c r="N33">
-        <v>187.5382571999999</v>
+        <v>185.6628784</v>
       </c>
       <c r="O33">
-        <v>18.75382571999999</v>
+        <v>18.56628784</v>
       </c>
       <c r="P33">
-        <v>168.78443148</v>
+        <v>167.09659056</v>
       </c>
       <c r="Q33">
-        <v>277.98443148</v>
+        <v>276.2965905599999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1131892827994542</v>
+        <v>0.1141097337573779</v>
       </c>
       <c r="T33">
-        <v>1.350727870541826</v>
+        <v>1.369177076568167</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.225812939764488</v>
+        <v>4.093756285396847</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09424101895501695</v>
+        <v>0.09529473277841054</v>
       </c>
       <c r="C34">
-        <v>2284.255148843276</v>
+        <v>2185.681524140109</v>
       </c>
       <c r="D34">
-        <v>3106.127148843276</v>
+        <v>3039.999524140109</v>
       </c>
       <c r="E34">
-        <v>-507.4279999999999</v>
+        <v>-474.982</v>
       </c>
       <c r="F34">
-        <v>1038.272</v>
+        <v>1070.718</v>
       </c>
       <c r="G34">
         <v>216.4</v>
@@ -4069,45 +4069,45 @@
         <v>245.675</v>
       </c>
       <c r="M34">
-        <v>60.01212160000001</v>
+        <v>65.63501340000001</v>
       </c>
       <c r="N34">
-        <v>185.6628784</v>
+        <v>180.0399866</v>
       </c>
       <c r="O34">
-        <v>18.56628784</v>
+        <v>18.00399866</v>
       </c>
       <c r="P34">
-        <v>167.09659056</v>
+        <v>162.03598794</v>
       </c>
       <c r="Q34">
-        <v>276.2965905599999</v>
+        <v>271.23598794</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1141097337573779</v>
+        <v>0.1150576608632993</v>
       </c>
       <c r="T34">
-        <v>1.369177076568167</v>
+        <v>1.388177005162458</v>
       </c>
       <c r="U34">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V34">
         <v>0.1</v>
       </c>
       <c r="W34">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.093756285396847</v>
+        <v>3.74304791411835</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09529473277841054</v>
+        <v>0.09534044660180412</v>
       </c>
       <c r="C35">
-        <v>2185.681524140109</v>
+        <v>2150.430341488444</v>
       </c>
       <c r="D35">
-        <v>3039.999524140109</v>
+        <v>3037.194341488444</v>
       </c>
       <c r="E35">
-        <v>-474.982</v>
+        <v>-442.5359999999998</v>
       </c>
       <c r="F35">
-        <v>1070.718</v>
+        <v>1103.164</v>
       </c>
       <c r="G35">
         <v>216.4</v>
@@ -4151,28 +4151,28 @@
         <v>245.675</v>
       </c>
       <c r="M35">
-        <v>65.63501340000001</v>
+        <v>67.62395320000002</v>
       </c>
       <c r="N35">
-        <v>180.0399866</v>
+        <v>178.0510467999999</v>
       </c>
       <c r="O35">
-        <v>18.00399866</v>
+        <v>17.80510468</v>
       </c>
       <c r="P35">
-        <v>162.03598794</v>
+        <v>160.2459421199999</v>
       </c>
       <c r="Q35">
-        <v>271.23598794</v>
+        <v>269.4459421199999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1150576608632993</v>
+        <v>0.1160343130330365</v>
       </c>
       <c r="T35">
-        <v>1.388177005162458</v>
+        <v>1.407752689168698</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.74304791411835</v>
+        <v>3.632958269585457</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09534044660180412</v>
+        <v>0.09538616042519769</v>
       </c>
       <c r="C36">
-        <v>2150.430341488444</v>
+        <v>2115.184331071259</v>
       </c>
       <c r="D36">
-        <v>3037.194341488444</v>
+        <v>3034.394331071259</v>
       </c>
       <c r="E36">
-        <v>-442.5359999999998</v>
+        <v>-410.0899999999999</v>
       </c>
       <c r="F36">
-        <v>1103.164</v>
+        <v>1135.61</v>
       </c>
       <c r="G36">
         <v>216.4</v>
@@ -4233,28 +4233,28 @@
         <v>245.675</v>
       </c>
       <c r="M36">
-        <v>67.62395320000002</v>
+        <v>69.61289300000001</v>
       </c>
       <c r="N36">
-        <v>178.0510467999999</v>
+        <v>176.0621069999999</v>
       </c>
       <c r="O36">
-        <v>17.80510468</v>
+        <v>17.60621069999999</v>
       </c>
       <c r="P36">
-        <v>160.2459421199999</v>
+        <v>158.4558962999999</v>
       </c>
       <c r="Q36">
-        <v>269.4459421199999</v>
+        <v>267.6558962999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1160343130330365</v>
+        <v>0.1170410160387657</v>
       </c>
       <c r="T36">
-        <v>1.407752689168698</v>
+        <v>1.427930701913591</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.632958269585457</v>
+        <v>3.529159461883015</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09538616042519769</v>
+        <v>0.09633907424859127</v>
       </c>
       <c r="C37">
-        <v>2115.184331071259</v>
+        <v>2025.524851269826</v>
       </c>
       <c r="D37">
-        <v>3034.394331071259</v>
+        <v>2977.180851269826</v>
       </c>
       <c r="E37">
-        <v>-410.0899999999999</v>
+        <v>-377.6439999999998</v>
       </c>
       <c r="F37">
-        <v>1135.61</v>
+        <v>1168.056</v>
       </c>
       <c r="G37">
         <v>216.4</v>
@@ -4315,45 +4315,45 @@
         <v>245.675</v>
       </c>
       <c r="M37">
-        <v>69.61289300000001</v>
+        <v>74.87238960000002</v>
       </c>
       <c r="N37">
-        <v>176.0621069999999</v>
+        <v>170.8026103999999</v>
       </c>
       <c r="O37">
-        <v>17.60621069999999</v>
+        <v>17.08026103999999</v>
       </c>
       <c r="P37">
-        <v>158.4558962999999</v>
+        <v>153.72234936</v>
       </c>
       <c r="Q37">
-        <v>267.6558962999999</v>
+        <v>262.9223493599999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1170410160387657</v>
+        <v>0.1180791785134239</v>
       </c>
       <c r="T37">
-        <v>1.427930701913591</v>
+        <v>1.448739277556761</v>
       </c>
       <c r="U37">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V37">
         <v>0.1</v>
       </c>
       <c r="W37">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.529159461883015</v>
+        <v>3.281249621021844</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09633907424859128</v>
+        <v>0.09640998807198485</v>
       </c>
       <c r="C38">
-        <v>2025.524851269825</v>
+        <v>1988.907277927477</v>
       </c>
       <c r="D38">
-        <v>2977.180851269825</v>
+        <v>2973.009277927477</v>
       </c>
       <c r="E38">
-        <v>-377.644</v>
+        <v>-345.1979999999999</v>
       </c>
       <c r="F38">
-        <v>1168.056</v>
+        <v>1200.502</v>
       </c>
       <c r="G38">
         <v>216.4</v>
@@ -4397,28 +4397,28 @@
         <v>245.675</v>
       </c>
       <c r="M38">
-        <v>74.87238960000001</v>
+        <v>76.95217820000002</v>
       </c>
       <c r="N38">
-        <v>170.8026103999999</v>
+        <v>168.7228217999999</v>
       </c>
       <c r="O38">
-        <v>17.08026103999999</v>
+        <v>16.87228218</v>
       </c>
       <c r="P38">
-        <v>153.72234936</v>
+        <v>151.8505396199999</v>
       </c>
       <c r="Q38">
-        <v>262.9223493599999</v>
+        <v>261.0505396199999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1180791785134239</v>
+        <v>0.1191502985269601</v>
       </c>
       <c r="T38">
-        <v>1.448739277556761</v>
+        <v>1.47020844290289</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.281249621021845</v>
+        <v>3.192567198832065</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09640998807198485</v>
+        <v>0.09648090189537843</v>
       </c>
       <c r="C39">
-        <v>1988.907277927477</v>
+        <v>1952.301378497951</v>
       </c>
       <c r="D39">
-        <v>2973.009277927477</v>
+        <v>2968.849378497951</v>
       </c>
       <c r="E39">
-        <v>-345.1979999999999</v>
+        <v>-312.752</v>
       </c>
       <c r="F39">
-        <v>1200.502</v>
+        <v>1232.948</v>
       </c>
       <c r="G39">
         <v>216.4</v>
@@ -4479,28 +4479,28 @@
         <v>245.675</v>
       </c>
       <c r="M39">
-        <v>76.95217820000002</v>
+        <v>79.03196680000001</v>
       </c>
       <c r="N39">
-        <v>168.7228217999999</v>
+        <v>166.6430331999999</v>
       </c>
       <c r="O39">
-        <v>16.87228218</v>
+        <v>16.66430331999999</v>
       </c>
       <c r="P39">
-        <v>151.8505396199999</v>
+        <v>149.9787298799999</v>
       </c>
       <c r="Q39">
-        <v>261.0505396199999</v>
+        <v>259.1787298799999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1191502985269601</v>
+        <v>0.1202559707989975</v>
       </c>
       <c r="T39">
-        <v>1.47020844290289</v>
+        <v>1.492370161969861</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.192567198832065</v>
+        <v>3.108552272547011</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09648090189537843</v>
+        <v>0.09655181571877201</v>
       </c>
       <c r="C40">
-        <v>1952.301378497951</v>
+        <v>1915.707104046539</v>
       </c>
       <c r="D40">
-        <v>2968.849378497951</v>
+        <v>2964.70110404654</v>
       </c>
       <c r="E40">
-        <v>-312.752</v>
+        <v>-280.3059999999998</v>
       </c>
       <c r="F40">
-        <v>1232.948</v>
+        <v>1265.394</v>
       </c>
       <c r="G40">
         <v>216.4</v>
@@ -4561,28 +4561,28 @@
         <v>245.675</v>
       </c>
       <c r="M40">
-        <v>79.03196680000001</v>
+        <v>81.11175540000002</v>
       </c>
       <c r="N40">
-        <v>166.6430331999999</v>
+        <v>164.5632445999999</v>
       </c>
       <c r="O40">
-        <v>16.66430331999999</v>
+        <v>16.45632445999999</v>
       </c>
       <c r="P40">
-        <v>149.9787298799999</v>
+        <v>148.1069201399999</v>
       </c>
       <c r="Q40">
-        <v>259.1787298799999</v>
+        <v>257.3069201399999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1202559707989975</v>
+        <v>0.1213978946209377</v>
       </c>
       <c r="T40">
-        <v>1.492370161969861</v>
+        <v>1.515258494776734</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.108552272547011</v>
+        <v>3.028845804020164</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09655181571877201</v>
+        <v>0.09943072954216559</v>
       </c>
       <c r="C41">
-        <v>1915.707104046539</v>
+        <v>1724.11504984343</v>
       </c>
       <c r="D41">
-        <v>2964.70110404654</v>
+        <v>2805.55504984343</v>
       </c>
       <c r="E41">
-        <v>-280.3059999999998</v>
+        <v>-247.8599999999999</v>
       </c>
       <c r="F41">
-        <v>1265.394</v>
+        <v>1297.84</v>
       </c>
       <c r="G41">
         <v>216.4</v>
@@ -4643,45 +4643,45 @@
         <v>245.675</v>
       </c>
       <c r="M41">
-        <v>81.11175540000002</v>
+        <v>93.31469600000001</v>
       </c>
       <c r="N41">
-        <v>164.5632445999999</v>
+        <v>152.3603039999999</v>
       </c>
       <c r="O41">
-        <v>16.45632445999999</v>
+        <v>15.23603039999999</v>
       </c>
       <c r="P41">
-        <v>148.1069201399999</v>
+        <v>137.1242735999999</v>
       </c>
       <c r="Q41">
-        <v>257.3069201399999</v>
+        <v>246.3242735999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1213978946209377</v>
+        <v>0.122577882570276</v>
       </c>
       <c r="T41">
-        <v>1.515258494776734</v>
+        <v>1.538909772010502</v>
       </c>
       <c r="U41">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V41">
         <v>0.1</v>
       </c>
       <c r="W41">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.028845804020164</v>
+        <v>2.632757866992353</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09943072954216559</v>
+        <v>0.09957184336555916</v>
       </c>
       <c r="C42">
-        <v>1724.11504984343</v>
+        <v>1684.306412168298</v>
       </c>
       <c r="D42">
-        <v>2805.55504984343</v>
+        <v>2798.192412168299</v>
       </c>
       <c r="E42">
-        <v>-247.8599999999999</v>
+        <v>-215.4139999999998</v>
       </c>
       <c r="F42">
-        <v>1297.84</v>
+        <v>1330.286</v>
       </c>
       <c r="G42">
         <v>216.4</v>
@@ -4725,28 +4725,28 @@
         <v>245.675</v>
       </c>
       <c r="M42">
-        <v>93.31469600000001</v>
+        <v>95.64756340000002</v>
       </c>
       <c r="N42">
-        <v>152.3603039999999</v>
+        <v>150.0274365999999</v>
       </c>
       <c r="O42">
-        <v>15.23603039999999</v>
+        <v>15.00274365999999</v>
       </c>
       <c r="P42">
-        <v>137.1242735999999</v>
+        <v>135.0246929399999</v>
       </c>
       <c r="Q42">
-        <v>246.3242735999999</v>
+        <v>244.2246929399999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.122577882570276</v>
+        <v>0.1237978701111172</v>
       </c>
       <c r="T42">
-        <v>1.538909772010502</v>
+        <v>1.563362787455584</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.632757866992353</v>
+        <v>2.568544260480345</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09957184336555916</v>
+        <v>0.09971295718895273</v>
       </c>
       <c r="C43">
-        <v>1684.306412168298</v>
+        <v>1644.53631698858</v>
       </c>
       <c r="D43">
-        <v>2798.192412168299</v>
+        <v>2790.86831698858</v>
       </c>
       <c r="E43">
-        <v>-215.4139999999998</v>
+        <v>-182.9679999999998</v>
       </c>
       <c r="F43">
-        <v>1330.286</v>
+        <v>1362.732</v>
       </c>
       <c r="G43">
         <v>216.4</v>
@@ -4807,28 +4807,28 @@
         <v>245.675</v>
       </c>
       <c r="M43">
-        <v>95.64756340000002</v>
+        <v>97.98043080000002</v>
       </c>
       <c r="N43">
-        <v>150.0274365999999</v>
+        <v>147.6945691999999</v>
       </c>
       <c r="O43">
-        <v>15.00274365999999</v>
+        <v>14.76945691999999</v>
       </c>
       <c r="P43">
-        <v>135.0246929399999</v>
+        <v>132.92511228</v>
       </c>
       <c r="Q43">
-        <v>244.2246929399999</v>
+        <v>242.1251122799999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1237978701111172</v>
+        <v>0.1250599261878496</v>
       </c>
       <c r="T43">
-        <v>1.563362787455584</v>
+        <v>1.588659010329807</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.568544260480345</v>
+        <v>2.507388444754622</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09971295718895273</v>
+        <v>0.1013633710123463</v>
       </c>
       <c r="C44">
-        <v>1644.53631698858</v>
+        <v>1529.192401226672</v>
       </c>
       <c r="D44">
-        <v>2790.86831698858</v>
+        <v>2707.970401226672</v>
       </c>
       <c r="E44">
-        <v>-182.9679999999998</v>
+        <v>-150.5219999999999</v>
       </c>
       <c r="F44">
-        <v>1362.732</v>
+        <v>1395.178</v>
       </c>
       <c r="G44">
         <v>216.4</v>
@@ -4889,45 +4889,45 @@
         <v>245.675</v>
       </c>
       <c r="M44">
-        <v>97.98043080000002</v>
+        <v>105.7544924</v>
       </c>
       <c r="N44">
-        <v>147.6945691999999</v>
+        <v>139.9205076</v>
       </c>
       <c r="O44">
-        <v>14.76945691999999</v>
+        <v>13.99205076</v>
       </c>
       <c r="P44">
-        <v>132.92511228</v>
+        <v>125.92845684</v>
       </c>
       <c r="Q44">
-        <v>242.1251122799999</v>
+        <v>235.12845684</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1250599261878495</v>
+        <v>0.1263662649339409</v>
       </c>
       <c r="T44">
-        <v>1.588659010329806</v>
+        <v>1.614842819971546</v>
       </c>
       <c r="U44">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V44">
         <v>0.1</v>
       </c>
       <c r="W44">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.507388444754622</v>
+        <v>2.323069161646318</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1013633710123463</v>
+        <v>0.1015395848357399</v>
       </c>
       <c r="C45">
-        <v>1529.192401226672</v>
+        <v>1488.185486762687</v>
       </c>
       <c r="D45">
-        <v>2707.970401226672</v>
+        <v>2699.409486762687</v>
       </c>
       <c r="E45">
-        <v>-150.5219999999999</v>
+        <v>-118.0759999999998</v>
       </c>
       <c r="F45">
-        <v>1395.178</v>
+        <v>1427.624</v>
       </c>
       <c r="G45">
         <v>216.4</v>
@@ -4971,28 +4971,28 @@
         <v>245.675</v>
       </c>
       <c r="M45">
-        <v>105.7544924</v>
+        <v>108.2138992</v>
       </c>
       <c r="N45">
-        <v>139.9205076</v>
+        <v>137.4611007999999</v>
       </c>
       <c r="O45">
-        <v>13.99205076</v>
+        <v>13.74611007999999</v>
       </c>
       <c r="P45">
-        <v>125.92845684</v>
+        <v>123.7149907199999</v>
       </c>
       <c r="Q45">
-        <v>235.12845684</v>
+        <v>232.9149907199999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1263662649339409</v>
+        <v>0.1277192586352498</v>
       </c>
       <c r="T45">
-        <v>1.614842819971546</v>
+        <v>1.641961765671919</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.323069161646318</v>
+        <v>2.270272135245265</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1015395848357399</v>
+        <v>0.1017157986591335</v>
       </c>
       <c r="C46">
-        <v>1488.185486762687</v>
+        <v>1447.232530267849</v>
       </c>
       <c r="D46">
-        <v>2699.409486762687</v>
+        <v>2690.902530267849</v>
       </c>
       <c r="E46">
-        <v>-118.0759999999998</v>
+        <v>-85.62999999999988</v>
       </c>
       <c r="F46">
-        <v>1427.624</v>
+        <v>1460.07</v>
       </c>
       <c r="G46">
         <v>216.4</v>
@@ -5053,28 +5053,28 @@
         <v>245.675</v>
       </c>
       <c r="M46">
-        <v>108.2138992</v>
+        <v>110.673306</v>
       </c>
       <c r="N46">
-        <v>137.4611007999999</v>
+        <v>135.0016939999999</v>
       </c>
       <c r="O46">
-        <v>13.74611007999999</v>
+        <v>13.50016939999999</v>
       </c>
       <c r="P46">
-        <v>123.7149907199999</v>
+        <v>121.5015245999999</v>
       </c>
       <c r="Q46">
-        <v>232.9149907199999</v>
+        <v>230.7015245999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1277192586352498</v>
+        <v>0.1291214521075154</v>
       </c>
       <c r="T46">
-        <v>1.641961765671919</v>
+        <v>1.670066854852306</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.270272135245265</v>
+        <v>2.219821643350926</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1017157986591335</v>
+        <v>0.1018920124825271</v>
       </c>
       <c r="C47">
-        <v>1447.232530267849</v>
+        <v>1406.333023213068</v>
       </c>
       <c r="D47">
-        <v>2690.902530267849</v>
+        <v>2682.449023213068</v>
       </c>
       <c r="E47">
-        <v>-85.62999999999988</v>
+        <v>-53.18399999999974</v>
       </c>
       <c r="F47">
-        <v>1460.07</v>
+        <v>1492.516</v>
       </c>
       <c r="G47">
         <v>216.4</v>
@@ -5135,28 +5135,28 @@
         <v>245.675</v>
       </c>
       <c r="M47">
-        <v>110.673306</v>
+        <v>113.1327128</v>
       </c>
       <c r="N47">
-        <v>135.0016939999999</v>
+        <v>132.5422871999999</v>
       </c>
       <c r="O47">
-        <v>13.50016939999999</v>
+        <v>13.25422871999999</v>
       </c>
       <c r="P47">
-        <v>121.5015245999999</v>
+        <v>119.2880584799999</v>
       </c>
       <c r="Q47">
-        <v>230.7015245999999</v>
+        <v>228.4880584799999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1291214521075154</v>
+        <v>0.1305755786713464</v>
       </c>
       <c r="T47">
-        <v>1.670066854852306</v>
+        <v>1.699212873261595</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.219821643350926</v>
+        <v>2.171564651104167</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1018920124825271</v>
+        <v>0.1020682263059206</v>
       </c>
       <c r="C48">
-        <v>1406.333023213068</v>
+        <v>1365.486463439443</v>
       </c>
       <c r="D48">
-        <v>2682.449023213068</v>
+        <v>2674.048463439443</v>
       </c>
       <c r="E48">
-        <v>-53.18399999999974</v>
+        <v>-20.73799999999983</v>
       </c>
       <c r="F48">
-        <v>1492.516</v>
+        <v>1524.962</v>
       </c>
       <c r="G48">
         <v>216.4</v>
@@ -5217,28 +5217,28 @@
         <v>245.675</v>
       </c>
       <c r="M48">
-        <v>113.1327128</v>
+        <v>115.5921196</v>
       </c>
       <c r="N48">
-        <v>132.5422871999999</v>
+        <v>130.0828803999999</v>
       </c>
       <c r="O48">
-        <v>13.25422871999999</v>
+        <v>13.00828803999999</v>
       </c>
       <c r="P48">
-        <v>119.2880584799999</v>
+        <v>117.0745923599999</v>
       </c>
       <c r="Q48">
-        <v>228.4880584799999</v>
+        <v>226.2745923599999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1305755786713464</v>
+        <v>0.1320845779356993</v>
       </c>
       <c r="T48">
-        <v>1.699212873261595</v>
+        <v>1.729458741422179</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.171564651104167</v>
+        <v>2.125361147889184</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1020682263059206</v>
+        <v>0.1022444401293142</v>
       </c>
       <c r="C49">
-        <v>1365.486463439443</v>
+        <v>1324.692355058832</v>
       </c>
       <c r="D49">
-        <v>2674.048463439443</v>
+        <v>2665.700355058832</v>
       </c>
       <c r="E49">
-        <v>-20.73799999999983</v>
+        <v>11.70800000000031</v>
       </c>
       <c r="F49">
-        <v>1524.962</v>
+        <v>1557.408</v>
       </c>
       <c r="G49">
         <v>216.4</v>
@@ -5299,28 +5299,28 @@
         <v>245.675</v>
       </c>
       <c r="M49">
-        <v>115.5921196</v>
+        <v>118.0515264</v>
       </c>
       <c r="N49">
-        <v>130.0828803999999</v>
+        <v>127.6234735999999</v>
       </c>
       <c r="O49">
-        <v>13.00828803999999</v>
+        <v>12.76234735999999</v>
       </c>
       <c r="P49">
-        <v>117.0745923599999</v>
+        <v>114.8611262399999</v>
       </c>
       <c r="Q49">
-        <v>226.2745923599999</v>
+        <v>224.0611262399999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1320845779356993</v>
+        <v>0.1336516156332966</v>
       </c>
       <c r="T49">
-        <v>1.729458741422179</v>
+        <v>1.760867912204324</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.125361147889184</v>
+        <v>2.081082790641493</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1022444401293142</v>
+        <v>0.1024206539527078</v>
       </c>
       <c r="C50">
-        <v>1324.692355058833</v>
+        <v>1283.950208356273</v>
       </c>
       <c r="D50">
-        <v>2665.700355058833</v>
+        <v>2657.404208356273</v>
       </c>
       <c r="E50">
-        <v>11.70800000000008</v>
+        <v>44.154</v>
       </c>
       <c r="F50">
-        <v>1557.408</v>
+        <v>1589.854</v>
       </c>
       <c r="G50">
         <v>216.4</v>
@@ -5381,28 +5381,28 @@
         <v>245.675</v>
       </c>
       <c r="M50">
-        <v>118.0515264</v>
+        <v>120.5109332</v>
       </c>
       <c r="N50">
-        <v>127.6234735999999</v>
+        <v>125.1640667999999</v>
       </c>
       <c r="O50">
-        <v>12.76234735999999</v>
+        <v>12.51640668</v>
       </c>
       <c r="P50">
-        <v>114.8611262399999</v>
+        <v>112.64766012</v>
       </c>
       <c r="Q50">
-        <v>224.0611262399999</v>
+        <v>221.8476601199999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1336516156332965</v>
+        <v>0.1352801057896231</v>
       </c>
       <c r="T50">
-        <v>1.760867912204324</v>
+        <v>1.793508815174004</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.081082790641493</v>
+        <v>2.038611713281463</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1024206539527078</v>
+        <v>0.1089868677761014</v>
       </c>
       <c r="C51">
-        <v>1283.950208356273</v>
+        <v>975.3537223235903</v>
       </c>
       <c r="D51">
-        <v>2657.404208356273</v>
+        <v>2381.25372232359</v>
       </c>
       <c r="E51">
-        <v>44.154</v>
+        <v>76.60000000000014</v>
       </c>
       <c r="F51">
-        <v>1589.854</v>
+        <v>1622.3</v>
       </c>
       <c r="G51">
         <v>216.4</v>
@@ -5463,45 +5463,45 @@
         <v>245.675</v>
       </c>
       <c r="M51">
-        <v>120.5109332</v>
+        <v>146.007</v>
       </c>
       <c r="N51">
-        <v>125.1640667999999</v>
+        <v>99.66799999999995</v>
       </c>
       <c r="O51">
-        <v>12.51640668</v>
+        <v>9.966799999999996</v>
       </c>
       <c r="P51">
-        <v>112.64766012</v>
+        <v>89.70119999999996</v>
       </c>
       <c r="Q51">
-        <v>221.8476601199999</v>
+        <v>198.9012</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1352801057896231</v>
+        <v>0.1369737355522027</v>
       </c>
       <c r="T51">
-        <v>1.793508815174004</v>
+        <v>1.827455354262471</v>
       </c>
       <c r="U51">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V51">
         <v>0.1</v>
       </c>
       <c r="W51">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.038611713281463</v>
+        <v>1.682624805660002</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1089868677761014</v>
+        <v>0.1092908815994949</v>
       </c>
       <c r="C52">
-        <v>975.3537223235903</v>
+        <v>931.5055488089686</v>
       </c>
       <c r="D52">
-        <v>2381.25372232359</v>
+        <v>2369.851548808969</v>
       </c>
       <c r="E52">
-        <v>76.60000000000014</v>
+        <v>109.0460000000003</v>
       </c>
       <c r="F52">
-        <v>1622.3</v>
+        <v>1654.746</v>
       </c>
       <c r="G52">
         <v>216.4</v>
@@ -5545,28 +5545,28 @@
         <v>245.675</v>
       </c>
       <c r="M52">
-        <v>146.007</v>
+        <v>148.92714</v>
       </c>
       <c r="N52">
-        <v>99.66799999999995</v>
+        <v>96.74785999999992</v>
       </c>
       <c r="O52">
-        <v>9.966799999999996</v>
+        <v>9.674785999999992</v>
       </c>
       <c r="P52">
-        <v>89.70119999999996</v>
+        <v>87.07307399999992</v>
       </c>
       <c r="Q52">
-        <v>198.9012</v>
+        <v>196.2730739999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1369737355522027</v>
+        <v>0.1387364930601937</v>
       </c>
       <c r="T52">
-        <v>1.827455354262471</v>
+        <v>1.862787466374956</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.682624805660002</v>
+        <v>1.649632162411767</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1092908815994949</v>
+        <v>0.1095948954228885</v>
       </c>
       <c r="C53">
-        <v>931.5055488089686</v>
+        <v>887.7660491417494</v>
       </c>
       <c r="D53">
-        <v>2369.851548808969</v>
+        <v>2358.55804914175</v>
       </c>
       <c r="E53">
-        <v>109.0460000000003</v>
+        <v>141.4920000000002</v>
       </c>
       <c r="F53">
-        <v>1654.746</v>
+        <v>1687.192</v>
       </c>
       <c r="G53">
         <v>216.4</v>
@@ -5627,28 +5627,28 @@
         <v>245.675</v>
       </c>
       <c r="M53">
-        <v>148.92714</v>
+        <v>151.84728</v>
       </c>
       <c r="N53">
-        <v>96.74785999999992</v>
+        <v>93.82771999999994</v>
       </c>
       <c r="O53">
-        <v>9.674785999999992</v>
+        <v>9.382771999999994</v>
       </c>
       <c r="P53">
-        <v>87.07307399999992</v>
+        <v>84.44494799999995</v>
       </c>
       <c r="Q53">
-        <v>196.2730739999999</v>
+        <v>193.6449479999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1387364930601937</v>
+        <v>0.1405726987976844</v>
       </c>
       <c r="T53">
-        <v>1.862787466374956</v>
+        <v>1.899591749825463</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.649632162411767</v>
+        <v>1.617908466980771</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1095948954228885</v>
+        <v>0.1098989092462821</v>
       </c>
       <c r="C54">
-        <v>887.7660491417494</v>
+        <v>844.1336770389066</v>
       </c>
       <c r="D54">
-        <v>2358.55804914175</v>
+        <v>2347.371677038907</v>
       </c>
       <c r="E54">
-        <v>141.4920000000002</v>
+        <v>173.9380000000003</v>
       </c>
       <c r="F54">
-        <v>1687.192</v>
+        <v>1719.638</v>
       </c>
       <c r="G54">
         <v>216.4</v>
@@ -5709,28 +5709,28 @@
         <v>245.675</v>
       </c>
       <c r="M54">
-        <v>151.84728</v>
+        <v>154.76742</v>
       </c>
       <c r="N54">
-        <v>93.82771999999994</v>
+        <v>90.90757999999994</v>
       </c>
       <c r="O54">
-        <v>9.382771999999994</v>
+        <v>9.090757999999994</v>
       </c>
       <c r="P54">
-        <v>84.44494799999995</v>
+        <v>81.81682199999995</v>
       </c>
       <c r="Q54">
-        <v>193.6449479999999</v>
+        <v>191.0168219999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1405726987976844</v>
+        <v>0.1424870409495363</v>
       </c>
       <c r="T54">
-        <v>1.899591749825463</v>
+        <v>1.937962172997267</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.617908466980771</v>
+        <v>1.587381892132077</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1098989092462821</v>
+        <v>0.1102029230696757</v>
       </c>
       <c r="C55">
-        <v>844.1336770389066</v>
+        <v>800.6069154143092</v>
       </c>
       <c r="D55">
-        <v>2347.371677038907</v>
+        <v>2336.290915414309</v>
       </c>
       <c r="E55">
-        <v>173.9380000000003</v>
+        <v>206.3840000000002</v>
       </c>
       <c r="F55">
-        <v>1719.638</v>
+        <v>1752.084</v>
       </c>
       <c r="G55">
         <v>216.4</v>
@@ -5791,28 +5791,28 @@
         <v>245.675</v>
       </c>
       <c r="M55">
-        <v>154.76742</v>
+        <v>157.68756</v>
       </c>
       <c r="N55">
-        <v>90.90757999999994</v>
+        <v>87.98743999999994</v>
       </c>
       <c r="O55">
-        <v>9.090757999999994</v>
+        <v>8.798743999999994</v>
       </c>
       <c r="P55">
-        <v>81.81682199999995</v>
+        <v>79.18869599999994</v>
       </c>
       <c r="Q55">
-        <v>191.0168219999999</v>
+        <v>188.3886959999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1424870409495363</v>
+        <v>0.1444846153688601</v>
       </c>
       <c r="T55">
-        <v>1.937962172997267</v>
+        <v>1.978000875437411</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.587381892132077</v>
+        <v>1.557985931166669</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1102029230696757</v>
+        <v>0.1105069368930692</v>
       </c>
       <c r="C56">
-        <v>800.6069154143092</v>
+        <v>757.1842756928443</v>
       </c>
       <c r="D56">
-        <v>2336.290915414309</v>
+        <v>2325.314275692845</v>
       </c>
       <c r="E56">
-        <v>206.3840000000002</v>
+        <v>238.8300000000004</v>
       </c>
       <c r="F56">
-        <v>1752.084</v>
+        <v>1784.53</v>
       </c>
       <c r="G56">
         <v>216.4</v>
@@ -5873,28 +5873,28 @@
         <v>245.675</v>
       </c>
       <c r="M56">
-        <v>157.68756</v>
+        <v>160.6077</v>
       </c>
       <c r="N56">
-        <v>87.98743999999994</v>
+        <v>85.06729999999993</v>
       </c>
       <c r="O56">
-        <v>8.798743999999994</v>
+        <v>8.506729999999994</v>
       </c>
       <c r="P56">
-        <v>79.18869599999994</v>
+        <v>76.56056999999994</v>
       </c>
       <c r="Q56">
-        <v>188.3886959999999</v>
+        <v>185.7605699999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1444846153688601</v>
+        <v>0.1465709708734872</v>
       </c>
       <c r="T56">
-        <v>1.978000875437411</v>
+        <v>2.019819075763784</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.557985931166669</v>
+        <v>1.529658914236365</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1105069368930692</v>
+        <v>0.1108109507164628</v>
       </c>
       <c r="C57">
-        <v>757.1842756928443</v>
+        <v>713.8642971437814</v>
       </c>
       <c r="D57">
-        <v>2325.314275692845</v>
+        <v>2314.440297143782</v>
       </c>
       <c r="E57">
-        <v>238.8300000000004</v>
+        <v>271.2760000000003</v>
       </c>
       <c r="F57">
-        <v>1784.53</v>
+        <v>1816.976</v>
       </c>
       <c r="G57">
         <v>216.4</v>
@@ -5955,28 +5955,28 @@
         <v>245.675</v>
       </c>
       <c r="M57">
-        <v>160.6077</v>
+        <v>163.52784</v>
       </c>
       <c r="N57">
-        <v>85.06729999999993</v>
+        <v>82.14715999999993</v>
       </c>
       <c r="O57">
-        <v>8.506729999999994</v>
+        <v>8.214715999999994</v>
       </c>
       <c r="P57">
-        <v>76.56056999999994</v>
+        <v>73.93244399999993</v>
       </c>
       <c r="Q57">
-        <v>185.7605699999999</v>
+        <v>183.1324439999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1465709708734872</v>
+        <v>0.1487521607192337</v>
       </c>
       <c r="T57">
-        <v>2.019819075763784</v>
+        <v>2.063538103377718</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.529658914236365</v>
+        <v>1.502343576482145</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1108109507164628</v>
+        <v>0.1413092812623533</v>
       </c>
       <c r="C58">
-        <v>713.8642971437814</v>
+        <v>-57.63621439763256</v>
       </c>
       <c r="D58">
-        <v>2314.440297143782</v>
+        <v>1575.385785602368</v>
       </c>
       <c r="E58">
-        <v>271.2760000000003</v>
+        <v>303.7220000000004</v>
       </c>
       <c r="F58">
-        <v>1816.976</v>
+        <v>1849.422</v>
       </c>
       <c r="G58">
         <v>216.4</v>
@@ -6037,45 +6037,45 @@
         <v>245.675</v>
       </c>
       <c r="M58">
-        <v>163.52784</v>
+        <v>271.4951496000001</v>
       </c>
       <c r="N58">
-        <v>82.14715999999993</v>
+        <v>-25.82014960000015</v>
       </c>
       <c r="O58">
-        <v>8.214715999999994</v>
+        <v>-2.582014960000015</v>
       </c>
       <c r="P58">
-        <v>73.93244399999993</v>
+        <v>-23.23813464000013</v>
       </c>
       <c r="Q58">
-        <v>183.1324439999999</v>
+        <v>85.96186535999985</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1487521607192337</v>
+        <v>0.1516397509019146</v>
       </c>
       <c r="T58">
-        <v>2.063538103377718</v>
+        <v>2.121415979152968</v>
       </c>
       <c r="U58">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1</v>
+        <v>0.09048964608095521</v>
       </c>
       <c r="W58">
-        <v>0.081</v>
+        <v>0.1335161199553158</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.502343576482145</v>
+        <v>0.904896460809552</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1413092812623533</v>
+        <v>0.1423192812623533</v>
       </c>
       <c r="C59">
-        <v>-57.63621439763256</v>
+        <v>-106.567414273225</v>
       </c>
       <c r="D59">
-        <v>1575.385785602368</v>
+        <v>1558.900585726775</v>
       </c>
       <c r="E59">
-        <v>303.7220000000004</v>
+        <v>336.1680000000003</v>
       </c>
       <c r="F59">
-        <v>1849.422</v>
+        <v>1881.868</v>
       </c>
       <c r="G59">
         <v>216.4</v>
@@ -6119,37 +6119,37 @@
         <v>245.675</v>
       </c>
       <c r="M59">
-        <v>271.4951496000001</v>
+        <v>276.2582224000001</v>
       </c>
       <c r="N59">
-        <v>-25.82014960000015</v>
+        <v>-30.58322240000012</v>
       </c>
       <c r="O59">
-        <v>-2.582014960000015</v>
+        <v>-3.058322240000013</v>
       </c>
       <c r="P59">
-        <v>-23.23813464000013</v>
+        <v>-27.52490016000011</v>
       </c>
       <c r="Q59">
-        <v>85.96186535999985</v>
+        <v>81.67509983999987</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1516397509019146</v>
+        <v>0.1541597449710078</v>
       </c>
       <c r="T59">
-        <v>2.121415979152968</v>
+        <v>2.171925883418515</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.09048964608095521</v>
+        <v>0.08892947976921461</v>
       </c>
       <c r="W59">
-        <v>0.1335161199553158</v>
+        <v>0.1337451523698793</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.904896460809552</v>
+        <v>0.889294797692146</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1423192812623532</v>
+        <v>0.1433292812623533</v>
       </c>
       <c r="C60">
-        <v>-106.5674142732244</v>
+        <v>-155.1571771637628</v>
       </c>
       <c r="D60">
-        <v>1558.900585726776</v>
+        <v>1542.756822836237</v>
       </c>
       <c r="E60">
-        <v>336.1680000000001</v>
+        <v>368.614</v>
       </c>
       <c r="F60">
-        <v>1881.868</v>
+        <v>1914.314</v>
       </c>
       <c r="G60">
         <v>216.4</v>
@@ -6201,37 +6201,37 @@
         <v>245.675</v>
       </c>
       <c r="M60">
-        <v>276.2582224</v>
+        <v>281.0212952000001</v>
       </c>
       <c r="N60">
-        <v>-30.58322240000007</v>
+        <v>-35.3462952000001</v>
       </c>
       <c r="O60">
-        <v>-3.058322240000007</v>
+        <v>-3.53462952000001</v>
       </c>
       <c r="P60">
-        <v>-27.52490016000006</v>
+        <v>-31.81166568000009</v>
       </c>
       <c r="Q60">
-        <v>81.67509983999993</v>
+        <v>77.3883343199999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1541597449710077</v>
+        <v>0.1568026655800567</v>
       </c>
       <c r="T60">
-        <v>2.171925883418515</v>
+        <v>2.224899685453112</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.08892947976921463</v>
+        <v>0.08742220045109234</v>
       </c>
       <c r="W60">
-        <v>0.1337451523698793</v>
+        <v>0.1339664209737797</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8892947976921463</v>
+        <v>0.8742220045109232</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1433292812623533</v>
+        <v>0.1443392812623532</v>
       </c>
       <c r="C61">
-        <v>-155.1571771637628</v>
+        <v>-203.416001969294</v>
       </c>
       <c r="D61">
-        <v>1542.756822836237</v>
+        <v>1526.943998030706</v>
       </c>
       <c r="E61">
-        <v>368.614</v>
+        <v>401.0600000000002</v>
       </c>
       <c r="F61">
-        <v>1914.314</v>
+        <v>1946.76</v>
       </c>
       <c r="G61">
         <v>216.4</v>
@@ -6283,37 +6283,37 @@
         <v>245.675</v>
       </c>
       <c r="M61">
-        <v>281.0212952000001</v>
+        <v>285.7843680000001</v>
       </c>
       <c r="N61">
-        <v>-35.3462952000001</v>
+        <v>-40.10936800000013</v>
       </c>
       <c r="O61">
-        <v>-3.53462952000001</v>
+        <v>-4.010936800000013</v>
       </c>
       <c r="P61">
-        <v>-31.81166568000009</v>
+        <v>-36.09843120000012</v>
       </c>
       <c r="Q61">
-        <v>77.3883343199999</v>
+        <v>73.10156879999987</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1568026655800567</v>
+        <v>0.1595777322195581</v>
       </c>
       <c r="T61">
-        <v>2.224899685453112</v>
+        <v>2.28052217758944</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.08742220045109234</v>
+        <v>0.08596516377690745</v>
       </c>
       <c r="W61">
-        <v>0.1339664209737797</v>
+        <v>0.13418031395755</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8742220045109232</v>
+        <v>0.8596516377690745</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1443392812623532</v>
+        <v>0.1453492812623533</v>
       </c>
       <c r="C62">
-        <v>-203.416001969294</v>
+        <v>-251.3539615139011</v>
       </c>
       <c r="D62">
-        <v>1526.943998030706</v>
+        <v>1511.452038486099</v>
       </c>
       <c r="E62">
-        <v>401.0600000000002</v>
+        <v>433.5060000000001</v>
       </c>
       <c r="F62">
-        <v>1946.76</v>
+        <v>1979.206</v>
       </c>
       <c r="G62">
         <v>216.4</v>
@@ -6365,37 +6365,37 @@
         <v>245.675</v>
       </c>
       <c r="M62">
-        <v>285.7843680000001</v>
+        <v>290.5474408000001</v>
       </c>
       <c r="N62">
-        <v>-40.10936800000013</v>
+        <v>-44.87244080000011</v>
       </c>
       <c r="O62">
-        <v>-4.010936800000013</v>
+        <v>-4.487244080000011</v>
       </c>
       <c r="P62">
-        <v>-36.09843120000012</v>
+        <v>-40.3851967200001</v>
       </c>
       <c r="Q62">
-        <v>73.10156879999987</v>
+        <v>68.81480327999989</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1595777322195581</v>
+        <v>0.1624951099687776</v>
       </c>
       <c r="T62">
-        <v>2.28052217758944</v>
+        <v>2.338997105219939</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.08596516377690745</v>
+        <v>0.08455589879695816</v>
       </c>
       <c r="W62">
-        <v>0.13418031395755</v>
+        <v>0.1343871940566066</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8596516377690745</v>
+        <v>0.8455589879695815</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1453492812623533</v>
+        <v>0.1463592812623533</v>
       </c>
       <c r="C63">
-        <v>-251.3539615139011</v>
+        <v>-298.9807239428626</v>
       </c>
       <c r="D63">
-        <v>1511.452038486099</v>
+        <v>1496.271276057138</v>
       </c>
       <c r="E63">
-        <v>433.5060000000001</v>
+        <v>465.9520000000002</v>
       </c>
       <c r="F63">
-        <v>1979.206</v>
+        <v>2011.652</v>
       </c>
       <c r="G63">
         <v>216.4</v>
@@ -6447,37 +6447,37 @@
         <v>245.675</v>
       </c>
       <c r="M63">
-        <v>290.5474408000001</v>
+        <v>295.3105136000001</v>
       </c>
       <c r="N63">
-        <v>-44.87244080000011</v>
+        <v>-49.63551360000014</v>
       </c>
       <c r="O63">
-        <v>-4.487244080000011</v>
+        <v>-4.963551360000015</v>
       </c>
       <c r="P63">
-        <v>-40.3851967200001</v>
+        <v>-44.67196224000013</v>
       </c>
       <c r="Q63">
-        <v>68.81480327999989</v>
+        <v>64.52803775999986</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1624951099687776</v>
+        <v>0.1655660339153243</v>
       </c>
       <c r="T63">
-        <v>2.338997105219939</v>
+        <v>2.400549660620463</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.08455589879695816</v>
+        <v>0.08319209397765237</v>
       </c>
       <c r="W63">
-        <v>0.1343871940566066</v>
+        <v>0.1345874006040806</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8455589879695815</v>
+        <v>0.8319209397765237</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1463592812623533</v>
+        <v>0.1473692812623533</v>
       </c>
       <c r="C64">
-        <v>-298.9807239428626</v>
+        <v>-346.3055728431932</v>
       </c>
       <c r="D64">
-        <v>1496.271276057138</v>
+        <v>1481.392427156807</v>
       </c>
       <c r="E64">
-        <v>465.9520000000002</v>
+        <v>498.3980000000001</v>
       </c>
       <c r="F64">
-        <v>2011.652</v>
+        <v>2044.098</v>
       </c>
       <c r="G64">
         <v>216.4</v>
@@ -6529,37 +6529,37 @@
         <v>245.675</v>
       </c>
       <c r="M64">
-        <v>295.3105136000001</v>
+        <v>300.0735864000001</v>
       </c>
       <c r="N64">
-        <v>-49.63551360000014</v>
+        <v>-54.39858640000011</v>
       </c>
       <c r="O64">
-        <v>-4.963551360000015</v>
+        <v>-5.439858640000011</v>
       </c>
       <c r="P64">
-        <v>-44.67196224000013</v>
+        <v>-48.9587277600001</v>
       </c>
       <c r="Q64">
-        <v>64.52803775999986</v>
+        <v>60.24127223999989</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1655660339153243</v>
+        <v>0.1688029537508736</v>
       </c>
       <c r="T64">
-        <v>2.400549660620463</v>
+        <v>2.465429381177773</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.08319209397765237</v>
+        <v>0.08187158454943567</v>
       </c>
       <c r="W64">
-        <v>0.1345874006040806</v>
+        <v>0.1347812513881429</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8319209397765237</v>
+        <v>0.8187158454943567</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1473692812623533</v>
+        <v>0.1483792812623533</v>
       </c>
       <c r="C65">
-        <v>-346.3055728431932</v>
+        <v>-393.3374261755218</v>
       </c>
       <c r="D65">
-        <v>1481.392427156807</v>
+        <v>1466.806573824478</v>
       </c>
       <c r="E65">
-        <v>498.3980000000001</v>
+        <v>530.8440000000003</v>
       </c>
       <c r="F65">
-        <v>2044.098</v>
+        <v>2076.544</v>
       </c>
       <c r="G65">
         <v>216.4</v>
@@ -6611,37 +6611,37 @@
         <v>245.675</v>
       </c>
       <c r="M65">
-        <v>300.0735864000001</v>
+        <v>304.8366592000001</v>
       </c>
       <c r="N65">
-        <v>-54.39858640000011</v>
+        <v>-59.16165920000014</v>
       </c>
       <c r="O65">
-        <v>-5.439858640000011</v>
+        <v>-5.916165920000015</v>
       </c>
       <c r="P65">
-        <v>-48.9587277600001</v>
+        <v>-53.24549328000013</v>
       </c>
       <c r="Q65">
-        <v>60.24127223999989</v>
+        <v>55.95450671999986</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1688029537508736</v>
+        <v>0.1722197024661757</v>
       </c>
       <c r="T65">
-        <v>2.465429381177773</v>
+        <v>2.533913530654934</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.08187158454943567</v>
+        <v>0.08059234104085074</v>
       </c>
       <c r="W65">
-        <v>0.1347812513881429</v>
+        <v>0.1349690443352031</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8187158454943567</v>
+        <v>0.8059234104085073</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1483792812623533</v>
+        <v>0.1851548914257216</v>
       </c>
       <c r="C66">
-        <v>-393.3374261755218</v>
+        <v>-812.8721475842517</v>
       </c>
       <c r="D66">
-        <v>1466.806573824478</v>
+        <v>1079.717852415748</v>
       </c>
       <c r="E66">
-        <v>530.8440000000003</v>
+        <v>563.2900000000002</v>
       </c>
       <c r="F66">
-        <v>2076.544</v>
+        <v>2108.99</v>
       </c>
       <c r="G66">
         <v>216.4</v>
@@ -6693,45 +6693,45 @@
         <v>245.675</v>
       </c>
       <c r="M66">
-        <v>304.8366592000001</v>
+        <v>423.485192</v>
       </c>
       <c r="N66">
-        <v>-59.16165920000014</v>
+        <v>-177.8101920000001</v>
       </c>
       <c r="O66">
-        <v>-5.916165920000015</v>
+        <v>-17.78101920000001</v>
       </c>
       <c r="P66">
-        <v>-53.24549328000013</v>
+        <v>-160.0291728000001</v>
       </c>
       <c r="Q66">
-        <v>55.95450671999986</v>
+        <v>-50.82917280000009</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1722197024661757</v>
+        <v>0.1777334372891188</v>
       </c>
       <c r="T66">
-        <v>2.533913530654934</v>
+        <v>2.644428956650632</v>
       </c>
       <c r="U66">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.08059234104085074</v>
+        <v>0.05801265419452965</v>
       </c>
       <c r="W66">
-        <v>0.1349690443352031</v>
+        <v>0.1891510590377385</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.8059234104085073</v>
+        <v>0.5801265419452964</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1851548914257216</v>
+        <v>0.1867048914257216</v>
       </c>
       <c r="C67">
-        <v>-812.8721475842517</v>
+        <v>-857.1953979359657</v>
       </c>
       <c r="D67">
-        <v>1079.717852415748</v>
+        <v>1067.840602064034</v>
       </c>
       <c r="E67">
-        <v>563.2900000000002</v>
+        <v>595.7360000000001</v>
       </c>
       <c r="F67">
-        <v>2108.99</v>
+        <v>2141.436</v>
       </c>
       <c r="G67">
         <v>216.4</v>
@@ -6775,37 +6775,37 @@
         <v>245.675</v>
       </c>
       <c r="M67">
-        <v>423.485192</v>
+        <v>430.0003488</v>
       </c>
       <c r="N67">
-        <v>-177.8101920000001</v>
+        <v>-184.3253488000001</v>
       </c>
       <c r="O67">
-        <v>-17.78101920000001</v>
+        <v>-18.43253488000001</v>
       </c>
       <c r="P67">
-        <v>-160.0291728000001</v>
+        <v>-165.8928139200001</v>
       </c>
       <c r="Q67">
-        <v>-50.82917280000009</v>
+        <v>-56.69281392000008</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1777334372891188</v>
+        <v>0.1816138325035046</v>
       </c>
       <c r="T67">
-        <v>2.644428956650632</v>
+        <v>2.722206278905062</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.05801265419452965</v>
+        <v>0.05713367458552163</v>
       </c>
       <c r="W67">
-        <v>0.1891510590377385</v>
+        <v>0.1893275581432273</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5801265419452964</v>
+        <v>0.5713367458552162</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1867048914257216</v>
+        <v>0.1882548914257215</v>
       </c>
       <c r="C68">
-        <v>-857.1953979359657</v>
+        <v>-901.2601841821531</v>
       </c>
       <c r="D68">
-        <v>1067.840602064034</v>
+        <v>1056.221815817847</v>
       </c>
       <c r="E68">
-        <v>595.7360000000001</v>
+        <v>628.1820000000005</v>
       </c>
       <c r="F68">
-        <v>2141.436</v>
+        <v>2173.882000000001</v>
       </c>
       <c r="G68">
         <v>216.4</v>
@@ -6857,37 +6857,37 @@
         <v>245.675</v>
       </c>
       <c r="M68">
-        <v>430.0003488</v>
+        <v>436.5155056000001</v>
       </c>
       <c r="N68">
-        <v>-184.3253488000001</v>
+        <v>-190.8405056000001</v>
       </c>
       <c r="O68">
-        <v>-18.43253488000001</v>
+        <v>-19.08405056000002</v>
       </c>
       <c r="P68">
-        <v>-165.8928139200001</v>
+        <v>-171.7564550400001</v>
       </c>
       <c r="Q68">
-        <v>-56.69281392000008</v>
+        <v>-62.55645504000015</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1816138325035046</v>
+        <v>0.185729403185429</v>
       </c>
       <c r="T68">
-        <v>2.722206278905062</v>
+        <v>2.804697378265821</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.05713367458552163</v>
+        <v>0.05628093317379741</v>
       </c>
       <c r="W68">
-        <v>0.1893275581432273</v>
+        <v>0.1894987886187015</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5713367458552162</v>
+        <v>0.5628093317379741</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1882548914257215</v>
+        <v>0.1898048914257216</v>
       </c>
       <c r="C69">
-        <v>-901.2601841821531</v>
+        <v>-945.0748522760571</v>
       </c>
       <c r="D69">
-        <v>1056.221815817847</v>
+        <v>1044.853147723943</v>
       </c>
       <c r="E69">
-        <v>628.1820000000005</v>
+        <v>660.6280000000004</v>
       </c>
       <c r="F69">
-        <v>2173.882000000001</v>
+        <v>2206.328</v>
       </c>
       <c r="G69">
         <v>216.4</v>
@@ -6939,37 +6939,37 @@
         <v>245.675</v>
       </c>
       <c r="M69">
-        <v>436.5155056000001</v>
+        <v>443.0306624000001</v>
       </c>
       <c r="N69">
-        <v>-190.8405056000001</v>
+        <v>-197.3556624000001</v>
       </c>
       <c r="O69">
-        <v>-19.08405056000002</v>
+        <v>-19.73556624000001</v>
       </c>
       <c r="P69">
-        <v>-171.7564550400001</v>
+        <v>-177.6200961600001</v>
       </c>
       <c r="Q69">
-        <v>-62.55645504000015</v>
+        <v>-68.42009616000013</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.185729403185429</v>
+        <v>0.1901021970349737</v>
       </c>
       <c r="T69">
-        <v>2.804697378265821</v>
+        <v>2.892344171336628</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.05628093317379741</v>
+        <v>0.0554532723918298</v>
       </c>
       <c r="W69">
-        <v>0.1894987886187015</v>
+        <v>0.1896649829037206</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5628093317379741</v>
+        <v>0.554532723918298</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1898048914257216</v>
+        <v>0.1913548914257216</v>
       </c>
       <c r="C70">
-        <v>-945.0748522760571</v>
+        <v>-988.6473926699164</v>
       </c>
       <c r="D70">
-        <v>1044.853147723943</v>
+        <v>1033.726607330084</v>
       </c>
       <c r="E70">
-        <v>660.6280000000004</v>
+        <v>693.0740000000003</v>
       </c>
       <c r="F70">
-        <v>2206.328</v>
+        <v>2238.774</v>
       </c>
       <c r="G70">
         <v>216.4</v>
@@ -7021,37 +7021,37 @@
         <v>245.675</v>
       </c>
       <c r="M70">
-        <v>443.0306624000001</v>
+        <v>449.5458192000001</v>
       </c>
       <c r="N70">
-        <v>-197.3556624000001</v>
+        <v>-203.8708192000001</v>
       </c>
       <c r="O70">
-        <v>-19.73556624000001</v>
+        <v>-20.38708192000001</v>
       </c>
       <c r="P70">
-        <v>-177.6200961600001</v>
+        <v>-183.4837372800001</v>
       </c>
       <c r="Q70">
-        <v>-68.42009616000013</v>
+        <v>-74.28373728000014</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1901021970349737</v>
+        <v>0.1947571066167471</v>
       </c>
       <c r="T70">
-        <v>2.892344171336628</v>
+        <v>2.985645596218455</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.0554532723918298</v>
+        <v>0.05464960177745546</v>
       </c>
       <c r="W70">
-        <v>0.1896649829037206</v>
+        <v>0.1898263599630869</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.554532723918298</v>
+        <v>0.5464960177745546</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1913548914257216</v>
+        <v>0.1929048914257216</v>
       </c>
       <c r="C71">
-        <v>-988.6473926699164</v>
+        <v>-1031.985459044002</v>
       </c>
       <c r="D71">
-        <v>1033.726607330084</v>
+        <v>1022.834540955998</v>
       </c>
       <c r="E71">
-        <v>693.0740000000003</v>
+        <v>725.5200000000002</v>
       </c>
       <c r="F71">
-        <v>2238.774</v>
+        <v>2271.22</v>
       </c>
       <c r="G71">
         <v>216.4</v>
@@ -7103,37 +7103,37 @@
         <v>245.675</v>
       </c>
       <c r="M71">
-        <v>449.5458192000001</v>
+        <v>456.060976</v>
       </c>
       <c r="N71">
-        <v>-203.8708192000001</v>
+        <v>-210.3859760000001</v>
       </c>
       <c r="O71">
-        <v>-20.38708192000001</v>
+        <v>-21.03859760000001</v>
       </c>
       <c r="P71">
-        <v>-183.4837372800001</v>
+        <v>-189.3473784000001</v>
       </c>
       <c r="Q71">
-        <v>-74.28373728000014</v>
+        <v>-80.14737840000009</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1947571066167471</v>
+        <v>0.1997223435039719</v>
       </c>
       <c r="T71">
-        <v>2.985645596218455</v>
+        <v>3.085167116092403</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.05464960177745546</v>
+        <v>0.05386889318063467</v>
       </c>
       <c r="W71">
-        <v>0.1898263599630869</v>
+        <v>0.1899831262493286</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5464960177745546</v>
+        <v>0.5386889318063468</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1929048914257216</v>
+        <v>0.1944548914257216</v>
       </c>
       <c r="C72">
-        <v>-1031.985459044002</v>
+        <v>-1075.096385863945</v>
       </c>
       <c r="D72">
-        <v>1022.834540955998</v>
+        <v>1012.169614136056</v>
       </c>
       <c r="E72">
-        <v>725.5200000000002</v>
+        <v>757.9660000000006</v>
       </c>
       <c r="F72">
-        <v>2271.22</v>
+        <v>2303.666000000001</v>
       </c>
       <c r="G72">
         <v>216.4</v>
@@ -7185,37 +7185,37 @@
         <v>245.675</v>
       </c>
       <c r="M72">
-        <v>456.060976</v>
+        <v>462.5761328000002</v>
       </c>
       <c r="N72">
-        <v>-210.3859760000001</v>
+        <v>-216.9011328000002</v>
       </c>
       <c r="O72">
-        <v>-21.03859760000001</v>
+        <v>-21.69011328000002</v>
       </c>
       <c r="P72">
-        <v>-189.3473784000001</v>
+        <v>-195.2110195200002</v>
       </c>
       <c r="Q72">
-        <v>-80.14737840000009</v>
+        <v>-86.01101952000019</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1997223435039719</v>
+        <v>0.2050300105213503</v>
       </c>
       <c r="T72">
-        <v>3.085167116092403</v>
+        <v>3.191552189061108</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.05386889318063467</v>
+        <v>0.05311017637527361</v>
       </c>
       <c r="W72">
-        <v>0.1899831262493286</v>
+        <v>0.1901354765838451</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5386889318063468</v>
+        <v>0.5311017637527361</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1944548914257216</v>
+        <v>0.1960048914257216</v>
       </c>
       <c r="C73">
-        <v>-1075.096385863944</v>
+        <v>-1117.987204850992</v>
       </c>
       <c r="D73">
-        <v>1012.169614136056</v>
+        <v>1001.724795149008</v>
       </c>
       <c r="E73">
-        <v>757.9660000000001</v>
+        <v>790.412</v>
       </c>
       <c r="F73">
-        <v>2303.666</v>
+        <v>2336.112</v>
       </c>
       <c r="G73">
         <v>216.4</v>
@@ -7267,37 +7267,37 @@
         <v>245.675</v>
       </c>
       <c r="M73">
-        <v>462.5761328</v>
+        <v>469.0912896</v>
       </c>
       <c r="N73">
-        <v>-216.9011328000001</v>
+        <v>-223.4162896000001</v>
       </c>
       <c r="O73">
-        <v>-21.69011328000001</v>
+        <v>-22.34162896000001</v>
       </c>
       <c r="P73">
-        <v>-195.2110195200001</v>
+        <v>-201.0746606400001</v>
       </c>
       <c r="Q73">
-        <v>-86.01101952000008</v>
+        <v>-91.87466064000009</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2050300105213503</v>
+        <v>0.2107167966113985</v>
       </c>
       <c r="T73">
-        <v>3.191552189061106</v>
+        <v>3.305536195813289</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.05311017637527363</v>
+        <v>0.05237253503672815</v>
       </c>
       <c r="W73">
-        <v>0.1901354765838451</v>
+        <v>0.190283594964625</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5311017637527362</v>
+        <v>0.5237253503672816</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1960048914257216</v>
+        <v>0.1975548914257216</v>
       </c>
       <c r="C74">
-        <v>-1117.987204850992</v>
+        <v>-1160.664660442926</v>
       </c>
       <c r="D74">
-        <v>1001.724795149008</v>
+        <v>991.493339557074</v>
       </c>
       <c r="E74">
-        <v>790.412</v>
+        <v>822.8579999999999</v>
       </c>
       <c r="F74">
-        <v>2336.112</v>
+        <v>2368.558</v>
       </c>
       <c r="G74">
         <v>216.4</v>
@@ -7349,37 +7349,37 @@
         <v>245.675</v>
       </c>
       <c r="M74">
-        <v>469.0912896</v>
+        <v>475.6064464</v>
       </c>
       <c r="N74">
-        <v>-223.4162896000001</v>
+        <v>-229.9314464000001</v>
       </c>
       <c r="O74">
-        <v>-22.34162896000001</v>
+        <v>-22.99314464000001</v>
       </c>
       <c r="P74">
-        <v>-201.0746606400001</v>
+        <v>-206.9383017600001</v>
       </c>
       <c r="Q74">
-        <v>-91.87466064000009</v>
+        <v>-97.73830176000007</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2107167966113985</v>
+        <v>0.2168248261155243</v>
       </c>
       <c r="T74">
-        <v>3.305536195813289</v>
+        <v>3.427963462324892</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.05237253503672815</v>
+        <v>0.05165510304992366</v>
       </c>
       <c r="W74">
-        <v>0.190283594964625</v>
+        <v>0.1904276553075753</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5237253503672816</v>
+        <v>0.5165510304992367</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1975548914257216</v>
+        <v>0.1991048914257215</v>
       </c>
       <c r="C75">
-        <v>-1160.664660442926</v>
+        <v>-1203.135224317054</v>
       </c>
       <c r="D75">
-        <v>991.493339557074</v>
+        <v>981.468775682946</v>
       </c>
       <c r="E75">
-        <v>822.8579999999999</v>
+        <v>855.3040000000003</v>
       </c>
       <c r="F75">
-        <v>2368.558</v>
+        <v>2401.004</v>
       </c>
       <c r="G75">
         <v>216.4</v>
@@ -7431,37 +7431,37 @@
         <v>245.675</v>
       </c>
       <c r="M75">
-        <v>475.6064464</v>
+        <v>482.1216032000001</v>
       </c>
       <c r="N75">
-        <v>-229.9314464000001</v>
+        <v>-236.4466032000001</v>
       </c>
       <c r="O75">
-        <v>-22.99314464000001</v>
+        <v>-23.64466032000001</v>
       </c>
       <c r="P75">
-        <v>-206.9383017600001</v>
+        <v>-212.8019428800001</v>
       </c>
       <c r="Q75">
-        <v>-97.73830176000007</v>
+        <v>-103.6019428800001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2168248261155243</v>
+        <v>0.2234027040430445</v>
       </c>
       <c r="T75">
-        <v>3.427963462324892</v>
+        <v>3.559808210875849</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.05165510304992366</v>
+        <v>0.05095706111681658</v>
       </c>
       <c r="W75">
-        <v>0.1904276553075753</v>
+        <v>0.1905678221277432</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5165510304992367</v>
+        <v>0.5095706111681657</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1991048914257215</v>
+        <v>0.2006548914257216</v>
       </c>
       <c r="C76">
-        <v>-1203.135224317054</v>
+        <v>-1245.405109041021</v>
       </c>
       <c r="D76">
-        <v>981.468775682946</v>
+        <v>971.6448909589798</v>
       </c>
       <c r="E76">
-        <v>855.3040000000003</v>
+        <v>887.7500000000002</v>
       </c>
       <c r="F76">
-        <v>2401.004</v>
+        <v>2433.45</v>
       </c>
       <c r="G76">
         <v>216.4</v>
@@ -7513,37 +7513,37 @@
         <v>245.675</v>
       </c>
       <c r="M76">
-        <v>482.1216032000001</v>
+        <v>488.6367600000001</v>
       </c>
       <c r="N76">
-        <v>-236.4466032000001</v>
+        <v>-242.9617600000001</v>
       </c>
       <c r="O76">
-        <v>-23.64466032000001</v>
+        <v>-24.29617600000002</v>
       </c>
       <c r="P76">
-        <v>-212.8019428800001</v>
+        <v>-218.6655840000001</v>
       </c>
       <c r="Q76">
-        <v>-103.6019428800001</v>
+        <v>-109.4655840000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2234027040430445</v>
+        <v>0.2305068122047663</v>
       </c>
       <c r="T76">
-        <v>3.559808210875849</v>
+        <v>3.702200539310884</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.05095706111681658</v>
+        <v>0.05027763363525903</v>
       </c>
       <c r="W76">
-        <v>0.1905678221277432</v>
+        <v>0.19070425116604</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5095706111681657</v>
+        <v>0.5027763363525902</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2006548914257216</v>
+        <v>0.2290734731663199</v>
       </c>
       <c r="C77">
-        <v>-1245.405109041021</v>
+        <v>-1428.515410205292</v>
       </c>
       <c r="D77">
-        <v>971.6448909589798</v>
+        <v>820.9805897947076</v>
       </c>
       <c r="E77">
-        <v>887.7500000000002</v>
+        <v>920.1960000000001</v>
       </c>
       <c r="F77">
-        <v>2433.45</v>
+        <v>2465.896</v>
       </c>
       <c r="G77">
         <v>216.4</v>
@@ -7595,45 +7595,45 @@
         <v>245.675</v>
       </c>
       <c r="M77">
-        <v>488.6367600000001</v>
+        <v>581.4582768</v>
       </c>
       <c r="N77">
-        <v>-242.9617600000001</v>
+        <v>-335.7832768000001</v>
       </c>
       <c r="O77">
-        <v>-24.29617600000002</v>
+        <v>-33.57832768000001</v>
       </c>
       <c r="P77">
-        <v>-218.6655840000001</v>
+        <v>-302.20494912</v>
       </c>
       <c r="Q77">
-        <v>-109.4655840000001</v>
+        <v>-193.00494912</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2305068122047663</v>
+        <v>0.2393220199657912</v>
       </c>
       <c r="T77">
-        <v>3.702200539310884</v>
+        <v>3.878889566301528</v>
       </c>
       <c r="U77">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05027763363525903</v>
+        <v>0.04225152685968266</v>
       </c>
       <c r="W77">
-        <v>0.19070425116604</v>
+        <v>0.2258370899664868</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.5027763363525902</v>
+        <v>0.4225152685968266</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2290734731663199</v>
+        <v>0.2309734731663199</v>
       </c>
       <c r="C78">
-        <v>-1428.515410205292</v>
+        <v>-1469.385203818586</v>
       </c>
       <c r="D78">
-        <v>820.9805897947076</v>
+        <v>812.5567961814141</v>
       </c>
       <c r="E78">
-        <v>920.1960000000001</v>
+        <v>952.6420000000005</v>
       </c>
       <c r="F78">
-        <v>2465.896</v>
+        <v>2498.342000000001</v>
       </c>
       <c r="G78">
         <v>216.4</v>
@@ -7677,37 +7677,37 @@
         <v>245.675</v>
       </c>
       <c r="M78">
-        <v>581.4582768</v>
+        <v>589.1090436000002</v>
       </c>
       <c r="N78">
-        <v>-335.7832768000001</v>
+        <v>-343.4340436000002</v>
       </c>
       <c r="O78">
-        <v>-33.57832768000001</v>
+        <v>-34.34340436000002</v>
       </c>
       <c r="P78">
-        <v>-302.20494912</v>
+        <v>-309.0906392400002</v>
       </c>
       <c r="Q78">
-        <v>-193.00494912</v>
+        <v>-199.8906392400002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2393220199657912</v>
+        <v>0.247736020833869</v>
       </c>
       <c r="T78">
-        <v>3.878889566301528</v>
+        <v>4.04753693874942</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04225152685968266</v>
+        <v>0.04170280573163482</v>
       </c>
       <c r="W78">
-        <v>0.2258370899664868</v>
+        <v>0.2259664784084805</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4225152685968266</v>
+        <v>0.4170280573163482</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2309734731663199</v>
+        <v>0.2328734731663198</v>
       </c>
       <c r="C79">
-        <v>-1469.385203818586</v>
+        <v>-1510.083885968622</v>
       </c>
       <c r="D79">
-        <v>812.5567961814141</v>
+        <v>804.3041140313788</v>
       </c>
       <c r="E79">
-        <v>952.6420000000005</v>
+        <v>985.0880000000004</v>
       </c>
       <c r="F79">
-        <v>2498.342000000001</v>
+        <v>2530.788</v>
       </c>
       <c r="G79">
         <v>216.4</v>
@@ -7759,37 +7759,37 @@
         <v>245.675</v>
       </c>
       <c r="M79">
-        <v>589.1090436000002</v>
+        <v>596.7598104000001</v>
       </c>
       <c r="N79">
-        <v>-343.4340436000002</v>
+        <v>-351.0848104000002</v>
       </c>
       <c r="O79">
-        <v>-34.34340436000002</v>
+        <v>-35.10848104000002</v>
       </c>
       <c r="P79">
-        <v>-309.0906392400002</v>
+        <v>-315.9763293600001</v>
       </c>
       <c r="Q79">
-        <v>-199.8906392400002</v>
+        <v>-206.7763293600001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.247736020833869</v>
+        <v>0.2569149308717722</v>
       </c>
       <c r="T79">
-        <v>4.04753693874942</v>
+        <v>4.231515890510758</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04170280573163482</v>
+        <v>0.04116815437610105</v>
       </c>
       <c r="W79">
-        <v>0.2259664784084805</v>
+        <v>0.2260925491981154</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4170280573163482</v>
+        <v>0.4116815437610105</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2328734731663198</v>
+        <v>0.2347734731663199</v>
       </c>
       <c r="C80">
-        <v>-1510.083885968622</v>
+        <v>-1550.616617884242</v>
       </c>
       <c r="D80">
-        <v>804.3041140313788</v>
+        <v>796.2173821157587</v>
       </c>
       <c r="E80">
-        <v>985.0880000000004</v>
+        <v>1017.534</v>
       </c>
       <c r="F80">
-        <v>2530.788</v>
+        <v>2563.234</v>
       </c>
       <c r="G80">
         <v>216.4</v>
@@ -7841,37 +7841,37 @@
         <v>245.675</v>
       </c>
       <c r="M80">
-        <v>596.7598104000001</v>
+        <v>604.4105772000001</v>
       </c>
       <c r="N80">
-        <v>-351.0848104000002</v>
+        <v>-358.7355772000002</v>
       </c>
       <c r="O80">
-        <v>-35.10848104000002</v>
+        <v>-35.87355772000002</v>
       </c>
       <c r="P80">
-        <v>-315.9763293600001</v>
+        <v>-322.8620194800002</v>
       </c>
       <c r="Q80">
-        <v>-206.7763293600001</v>
+        <v>-213.6620194800002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2569149308717722</v>
+        <v>0.2669680228180472</v>
       </c>
       <c r="T80">
-        <v>4.231515890510758</v>
+        <v>4.433016647201748</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04116815437610105</v>
+        <v>0.04064703849792255</v>
       </c>
       <c r="W80">
-        <v>0.2260925491981154</v>
+        <v>0.2262154283221899</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4116815437610105</v>
+        <v>0.4064703849792255</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2347734731663199</v>
+        <v>0.2366734731663199</v>
       </c>
       <c r="C81">
-        <v>-1550.616617884242</v>
+        <v>-1590.988355289888</v>
       </c>
       <c r="D81">
-        <v>796.2173821157587</v>
+        <v>788.2916447101128</v>
       </c>
       <c r="E81">
-        <v>1017.534</v>
+        <v>1049.98</v>
       </c>
       <c r="F81">
-        <v>2563.234</v>
+        <v>2595.68</v>
       </c>
       <c r="G81">
         <v>216.4</v>
@@ -7923,37 +7923,37 @@
         <v>245.675</v>
       </c>
       <c r="M81">
-        <v>604.4105772000001</v>
+        <v>612.0613440000001</v>
       </c>
       <c r="N81">
-        <v>-358.7355772000002</v>
+        <v>-366.3863440000001</v>
       </c>
       <c r="O81">
-        <v>-35.87355772000002</v>
+        <v>-36.63863440000002</v>
       </c>
       <c r="P81">
-        <v>-322.8620194800002</v>
+        <v>-329.7477096000001</v>
       </c>
       <c r="Q81">
-        <v>-213.6620194800002</v>
+        <v>-220.5477096000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2669680228180472</v>
+        <v>0.2780264239589494</v>
       </c>
       <c r="T81">
-        <v>4.433016647201748</v>
+        <v>4.654667479561835</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04064703849792255</v>
+        <v>0.04013895051669852</v>
       </c>
       <c r="W81">
-        <v>0.2262154283221899</v>
+        <v>0.2263352354681625</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4064703849792255</v>
+        <v>0.4013895051669852</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2366734731663199</v>
+        <v>0.2385734731663199</v>
       </c>
       <c r="C82">
-        <v>-1590.988355289888</v>
+        <v>-1631.203858532987</v>
       </c>
       <c r="D82">
-        <v>788.2916447101128</v>
+        <v>780.5221414670133</v>
       </c>
       <c r="E82">
-        <v>1049.98</v>
+        <v>1082.426000000001</v>
       </c>
       <c r="F82">
-        <v>2595.68</v>
+        <v>2628.126000000001</v>
       </c>
       <c r="G82">
         <v>216.4</v>
@@ -8005,37 +8005,37 @@
         <v>245.675</v>
       </c>
       <c r="M82">
-        <v>612.0613440000001</v>
+        <v>619.7121108000002</v>
       </c>
       <c r="N82">
-        <v>-366.3863440000001</v>
+        <v>-374.0371108000003</v>
       </c>
       <c r="O82">
-        <v>-36.63863440000002</v>
+        <v>-37.40371108000003</v>
       </c>
       <c r="P82">
-        <v>-329.7477096000001</v>
+        <v>-336.6333997200002</v>
       </c>
       <c r="Q82">
-        <v>-220.5477096000001</v>
+        <v>-227.4333997200002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2780264239589494</v>
+        <v>0.2902488673252099</v>
       </c>
       <c r="T82">
-        <v>4.654667479561835</v>
+        <v>4.899649978486142</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04013895051669852</v>
+        <v>0.03964340791772693</v>
       </c>
       <c r="W82">
-        <v>0.2263352354681625</v>
+        <v>0.226452084413</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4013895051669852</v>
+        <v>0.3964340791772692</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2385734731663199</v>
+        <v>0.2404734731663199</v>
       </c>
       <c r="C83">
-        <v>-1631.203858532987</v>
+        <v>-1671.267702118283</v>
       </c>
       <c r="D83">
-        <v>780.5221414670133</v>
+        <v>772.9042978817173</v>
       </c>
       <c r="E83">
-        <v>1082.426000000001</v>
+        <v>1114.872000000001</v>
       </c>
       <c r="F83">
-        <v>2628.126000000001</v>
+        <v>2660.572000000001</v>
       </c>
       <c r="G83">
         <v>216.4</v>
@@ -8087,37 +8087,37 @@
         <v>245.675</v>
       </c>
       <c r="M83">
-        <v>619.7121108000002</v>
+        <v>627.3628776000002</v>
       </c>
       <c r="N83">
-        <v>-374.0371108000003</v>
+        <v>-381.6878776000002</v>
       </c>
       <c r="O83">
-        <v>-37.40371108000003</v>
+        <v>-38.16878776000002</v>
       </c>
       <c r="P83">
-        <v>-336.6333997200002</v>
+        <v>-343.5190898400002</v>
       </c>
       <c r="Q83">
-        <v>-227.4333997200002</v>
+        <v>-234.3190898400002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2902488673252099</v>
+        <v>0.3038293599543883</v>
       </c>
       <c r="T83">
-        <v>4.899649978486142</v>
+        <v>5.171852755068706</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03964340791772693</v>
+        <v>0.03915995172360831</v>
       </c>
       <c r="W83">
-        <v>0.226452084413</v>
+        <v>0.2265660833835732</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3964340791772692</v>
+        <v>0.3915995172360831</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2404734731663199</v>
+        <v>0.2423734731663199</v>
       </c>
       <c r="C84">
-        <v>-1671.267702118283</v>
+        <v>-1711.18428368924</v>
       </c>
       <c r="D84">
-        <v>772.9042978817173</v>
+        <v>765.4337163107608</v>
       </c>
       <c r="E84">
-        <v>1114.872000000001</v>
+        <v>1147.318</v>
       </c>
       <c r="F84">
-        <v>2660.572000000001</v>
+        <v>2693.018</v>
       </c>
       <c r="G84">
         <v>216.4</v>
@@ -8169,37 +8169,37 @@
         <v>245.675</v>
       </c>
       <c r="M84">
-        <v>627.3628776000002</v>
+        <v>635.0136444000001</v>
       </c>
       <c r="N84">
-        <v>-381.6878776000002</v>
+        <v>-389.3386444000001</v>
       </c>
       <c r="O84">
-        <v>-38.16878776000002</v>
+        <v>-38.93386444000001</v>
       </c>
       <c r="P84">
-        <v>-343.5190898400002</v>
+        <v>-350.4047799600001</v>
       </c>
       <c r="Q84">
-        <v>-234.3190898400002</v>
+        <v>-241.2047799600001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3038293599543883</v>
+        <v>0.3190075575987641</v>
       </c>
       <c r="T84">
-        <v>5.171852755068706</v>
+        <v>5.476079387719807</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03915995172360831</v>
+        <v>0.03868814507633592</v>
       </c>
       <c r="W84">
-        <v>0.2265660833835732</v>
+        <v>0.226677335391</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3915995172360831</v>
+        <v>0.3868814507633592</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2423734731663199</v>
+        <v>0.2442734731663199</v>
       </c>
       <c r="C85">
-        <v>-1711.18428368924</v>
+        <v>-1750.957832493566</v>
       </c>
       <c r="D85">
-        <v>765.4337163107608</v>
+        <v>758.1061675064345</v>
       </c>
       <c r="E85">
-        <v>1147.318</v>
+        <v>1179.764</v>
       </c>
       <c r="F85">
-        <v>2693.018</v>
+        <v>2725.464</v>
       </c>
       <c r="G85">
         <v>216.4</v>
@@ -8251,37 +8251,37 @@
         <v>245.675</v>
       </c>
       <c r="M85">
-        <v>635.0136444000001</v>
+        <v>642.6644112000001</v>
       </c>
       <c r="N85">
-        <v>-389.3386444000001</v>
+        <v>-396.9894112000002</v>
       </c>
       <c r="O85">
-        <v>-38.93386444000001</v>
+        <v>-39.69894112000002</v>
       </c>
       <c r="P85">
-        <v>-350.4047799600001</v>
+        <v>-357.2904700800001</v>
       </c>
       <c r="Q85">
-        <v>-241.2047799600001</v>
+        <v>-248.0904700800002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3190075575987641</v>
+        <v>0.3360830299486869</v>
       </c>
       <c r="T85">
-        <v>5.476079387719807</v>
+        <v>5.818334349452296</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03868814507633592</v>
+        <v>0.03822757192066525</v>
       </c>
       <c r="W85">
-        <v>0.226677335391</v>
+        <v>0.2267859385411071</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3868814507633592</v>
+        <v>0.3822757192066526</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2442734731663199</v>
+        <v>0.2461734731663199</v>
       </c>
       <c r="C86">
-        <v>-1750.957832493566</v>
+        <v>-1790.592417367107</v>
       </c>
       <c r="D86">
-        <v>758.1061675064342</v>
+        <v>750.9175826328934</v>
       </c>
       <c r="E86">
-        <v>1179.764</v>
+        <v>1212.21</v>
       </c>
       <c r="F86">
-        <v>2725.464</v>
+        <v>2757.91</v>
       </c>
       <c r="G86">
         <v>216.4</v>
@@ -8333,37 +8333,37 @@
         <v>245.675</v>
       </c>
       <c r="M86">
-        <v>642.6644112000001</v>
+        <v>650.3151780000001</v>
       </c>
       <c r="N86">
-        <v>-396.9894112000002</v>
+        <v>-404.6401780000001</v>
       </c>
       <c r="O86">
-        <v>-39.69894112000002</v>
+        <v>-40.46401780000001</v>
       </c>
       <c r="P86">
-        <v>-357.2904700800001</v>
+        <v>-364.1761602000001</v>
       </c>
       <c r="Q86">
-        <v>-248.0904700800002</v>
+        <v>-254.9761602000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3360830299486867</v>
+        <v>0.3554352319452658</v>
       </c>
       <c r="T86">
-        <v>5.818334349452291</v>
+        <v>6.206223306082444</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03822757192066525</v>
+        <v>0.03777783578042215</v>
       </c>
       <c r="W86">
-        <v>0.2267859385411071</v>
+        <v>0.2268919863229765</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3822757192066526</v>
+        <v>0.3777783578042214</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2461734731663199</v>
+        <v>0.2480734731663199</v>
       </c>
       <c r="C87">
-        <v>-1790.592417367107</v>
+        <v>-1830.091954267763</v>
       </c>
       <c r="D87">
-        <v>750.9175826328934</v>
+        <v>743.8640457322372</v>
       </c>
       <c r="E87">
-        <v>1212.21</v>
+        <v>1244.656</v>
       </c>
       <c r="F87">
-        <v>2757.91</v>
+        <v>2790.356</v>
       </c>
       <c r="G87">
         <v>216.4</v>
@@ -8415,37 +8415,37 @@
         <v>245.675</v>
       </c>
       <c r="M87">
-        <v>650.3151780000001</v>
+        <v>657.9659448000001</v>
       </c>
       <c r="N87">
-        <v>-404.6401780000001</v>
+        <v>-412.2909448000001</v>
       </c>
       <c r="O87">
-        <v>-40.46401780000001</v>
+        <v>-41.22909448000001</v>
       </c>
       <c r="P87">
-        <v>-364.1761602000001</v>
+        <v>-371.0618503200001</v>
       </c>
       <c r="Q87">
-        <v>-254.9761602000001</v>
+        <v>-261.8618503200001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3554352319452658</v>
+        <v>0.3775520342270706</v>
       </c>
       <c r="T87">
-        <v>6.206223306082444</v>
+        <v>6.64952497080262</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03777783578042215</v>
+        <v>0.03733855862018467</v>
       </c>
       <c r="W87">
-        <v>0.2268919863229765</v>
+        <v>0.2269955678773605</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3777783578042214</v>
+        <v>0.3733855862018467</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2480734731663199</v>
+        <v>0.2499734731663199</v>
       </c>
       <c r="C88">
-        <v>-1830.091954267763</v>
+        <v>-1869.46021338876</v>
       </c>
       <c r="D88">
-        <v>743.8640457322372</v>
+        <v>736.9417866112406</v>
       </c>
       <c r="E88">
-        <v>1244.656</v>
+        <v>1277.102</v>
       </c>
       <c r="F88">
-        <v>2790.356</v>
+        <v>2822.802</v>
       </c>
       <c r="G88">
         <v>216.4</v>
@@ -8497,37 +8497,37 @@
         <v>245.675</v>
       </c>
       <c r="M88">
-        <v>657.9659448000001</v>
+        <v>665.6167116</v>
       </c>
       <c r="N88">
-        <v>-412.2909448000001</v>
+        <v>-419.9417116000001</v>
       </c>
       <c r="O88">
-        <v>-41.22909448000001</v>
+        <v>-41.99417116000001</v>
       </c>
       <c r="P88">
-        <v>-371.0618503200001</v>
+        <v>-377.9475404400001</v>
       </c>
       <c r="Q88">
-        <v>-261.8618503200001</v>
+        <v>-268.7475404400001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3775520342270706</v>
+        <v>0.4030714214753067</v>
       </c>
       <c r="T88">
-        <v>6.64952497080262</v>
+        <v>7.16102689163359</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03733855862018467</v>
+        <v>0.03690937978546991</v>
       </c>
       <c r="W88">
-        <v>0.2269955678773605</v>
+        <v>0.2270967682465862</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3733855862018467</v>
+        <v>0.3690937978546991</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2499734731663199</v>
+        <v>0.2518734731663199</v>
       </c>
       <c r="C89">
-        <v>-1869.46021338876</v>
+        <v>-1908.70082587841</v>
       </c>
       <c r="D89">
-        <v>736.9417866112406</v>
+        <v>730.1471741215905</v>
       </c>
       <c r="E89">
-        <v>1277.102</v>
+        <v>1309.548</v>
       </c>
       <c r="F89">
-        <v>2822.802</v>
+        <v>2855.248000000001</v>
       </c>
       <c r="G89">
         <v>216.4</v>
@@ -8579,37 +8579,37 @@
         <v>245.675</v>
       </c>
       <c r="M89">
-        <v>665.6167116</v>
+        <v>673.2674784000002</v>
       </c>
       <c r="N89">
-        <v>-419.9417116000001</v>
+        <v>-427.5924784000002</v>
       </c>
       <c r="O89">
-        <v>-41.99417116000001</v>
+        <v>-42.75924784000003</v>
       </c>
       <c r="P89">
-        <v>-377.9475404400001</v>
+        <v>-384.8332305600002</v>
       </c>
       <c r="Q89">
-        <v>-268.7475404400001</v>
+        <v>-275.6332305600002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4030714214753067</v>
+        <v>0.4328440399315824</v>
       </c>
       <c r="T89">
-        <v>7.16102689163359</v>
+        <v>7.757779132603057</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03690937978546991</v>
+        <v>0.03648995501518047</v>
       </c>
       <c r="W89">
-        <v>0.2270967682465862</v>
+        <v>0.2271956686074204</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3690937978546991</v>
+        <v>0.3648995501518048</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2518734731663199</v>
+        <v>0.2537734731663199</v>
       </c>
       <c r="C90">
-        <v>-1908.70082587841</v>
+        <v>-1947.817290191528</v>
       </c>
       <c r="D90">
-        <v>730.1471741215905</v>
+        <v>723.4767098084728</v>
       </c>
       <c r="E90">
-        <v>1309.548</v>
+        <v>1341.994</v>
       </c>
       <c r="F90">
-        <v>2855.248000000001</v>
+        <v>2887.694</v>
       </c>
       <c r="G90">
         <v>216.4</v>
@@ -8661,37 +8661,37 @@
         <v>245.675</v>
       </c>
       <c r="M90">
-        <v>673.2674784000002</v>
+        <v>680.9182452000001</v>
       </c>
       <c r="N90">
-        <v>-427.5924784000002</v>
+        <v>-435.2432452000002</v>
       </c>
       <c r="O90">
-        <v>-42.75924784000003</v>
+        <v>-43.52432452000002</v>
       </c>
       <c r="P90">
-        <v>-384.8332305600002</v>
+        <v>-391.7189206800001</v>
       </c>
       <c r="Q90">
-        <v>-275.6332305600002</v>
+        <v>-282.5189206800001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4328440399315824</v>
+        <v>0.4680298617435444</v>
       </c>
       <c r="T90">
-        <v>7.757779132603057</v>
+        <v>8.463031781021517</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03648995501518047</v>
+        <v>0.03607995552062788</v>
       </c>
       <c r="W90">
-        <v>0.2271956686074204</v>
+        <v>0.227292346488236</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3648995501518048</v>
+        <v>0.3607995552062788</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2537734731663199</v>
+        <v>0.2556734731663199</v>
       </c>
       <c r="C91">
-        <v>-1947.817290191528</v>
+        <v>-1986.812978095852</v>
       </c>
       <c r="D91">
-        <v>723.4767098084728</v>
+        <v>716.927021904148</v>
       </c>
       <c r="E91">
-        <v>1341.994</v>
+        <v>1374.44</v>
       </c>
       <c r="F91">
-        <v>2887.694</v>
+        <v>2920.14</v>
       </c>
       <c r="G91">
         <v>216.4</v>
@@ -8743,37 +8743,37 @@
         <v>245.675</v>
       </c>
       <c r="M91">
-        <v>680.9182452000001</v>
+        <v>688.5690120000002</v>
       </c>
       <c r="N91">
-        <v>-435.2432452000002</v>
+        <v>-442.8940120000002</v>
       </c>
       <c r="O91">
-        <v>-43.52432452000002</v>
+        <v>-44.28940120000002</v>
       </c>
       <c r="P91">
-        <v>-391.7189206800001</v>
+        <v>-398.6046108000002</v>
       </c>
       <c r="Q91">
-        <v>-282.5189206800001</v>
+        <v>-289.4046108000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4680298617435444</v>
+        <v>0.5102528479178988</v>
       </c>
       <c r="T91">
-        <v>8.463031781021517</v>
+        <v>9.309334959123669</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03607995552062788</v>
+        <v>0.03567906712595424</v>
       </c>
       <c r="W91">
-        <v>0.227292346488236</v>
+        <v>0.2273868759717</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3607995552062788</v>
+        <v>0.3567906712595423</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2556734731663199</v>
+        <v>0.2575734731663199</v>
       </c>
       <c r="C92">
-        <v>-1986.812978095852</v>
+        <v>-2025.691140355136</v>
       </c>
       <c r="D92">
-        <v>716.927021904148</v>
+        <v>710.4948596448642</v>
       </c>
       <c r="E92">
-        <v>1374.44</v>
+        <v>1406.886</v>
       </c>
       <c r="F92">
-        <v>2920.14</v>
+        <v>2952.586</v>
       </c>
       <c r="G92">
         <v>216.4</v>
@@ -8825,37 +8825,37 @@
         <v>245.675</v>
       </c>
       <c r="M92">
-        <v>688.5690120000002</v>
+        <v>696.2197788000001</v>
       </c>
       <c r="N92">
-        <v>-442.8940120000002</v>
+        <v>-450.5447788000001</v>
       </c>
       <c r="O92">
-        <v>-44.28940120000002</v>
+        <v>-45.05447788000001</v>
       </c>
       <c r="P92">
-        <v>-398.6046108000002</v>
+        <v>-405.4903009200001</v>
       </c>
       <c r="Q92">
-        <v>-289.4046108000002</v>
+        <v>-296.2903009200001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5102528479178988</v>
+        <v>0.5618587199087766</v>
       </c>
       <c r="T92">
-        <v>9.309334959123669</v>
+        <v>10.34370551013741</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03567906712595424</v>
+        <v>0.03528698946522947</v>
       </c>
       <c r="W92">
-        <v>0.2273868759717</v>
+        <v>0.2274793278840989</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3567906712595423</v>
+        <v>0.3528698946522947</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2575734731663199</v>
+        <v>0.2594734731663199</v>
       </c>
       <c r="C93">
-        <v>-2025.691140355136</v>
+        <v>-2064.454912109024</v>
       </c>
       <c r="D93">
-        <v>710.4948596448642</v>
+        <v>704.1770878909765</v>
       </c>
       <c r="E93">
-        <v>1406.886</v>
+        <v>1439.332000000001</v>
       </c>
       <c r="F93">
-        <v>2952.586</v>
+        <v>2985.032000000001</v>
       </c>
       <c r="G93">
         <v>216.4</v>
@@ -8907,37 +8907,37 @@
         <v>245.675</v>
       </c>
       <c r="M93">
-        <v>696.2197788000001</v>
+        <v>703.8705456000001</v>
       </c>
       <c r="N93">
-        <v>-450.5447788000001</v>
+        <v>-458.1955456000002</v>
       </c>
       <c r="O93">
-        <v>-45.05447788000001</v>
+        <v>-45.81955456000002</v>
       </c>
       <c r="P93">
-        <v>-405.4903009200001</v>
+        <v>-412.3759910400001</v>
       </c>
       <c r="Q93">
-        <v>-296.2903009200001</v>
+        <v>-303.1759910400002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5618587199087766</v>
+        <v>0.6263660598973738</v>
       </c>
       <c r="T93">
-        <v>10.34370551013741</v>
+        <v>11.63666869890459</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03528698946522947</v>
+        <v>0.03490343523191176</v>
       </c>
       <c r="W93">
-        <v>0.2274793278840989</v>
+        <v>0.2275697699723152</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3528698946522947</v>
+        <v>0.3490343523191176</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2594734731663199</v>
+        <v>0.2613734731663199</v>
       </c>
       <c r="C94">
-        <v>-2064.454912109024</v>
+        <v>-2103.107317968434</v>
       </c>
       <c r="D94">
-        <v>704.1770878909765</v>
+        <v>697.9706820315662</v>
       </c>
       <c r="E94">
-        <v>1439.332000000001</v>
+        <v>1471.778</v>
       </c>
       <c r="F94">
-        <v>2985.032000000001</v>
+        <v>3017.478000000001</v>
       </c>
       <c r="G94">
         <v>216.4</v>
@@ -8989,37 +8989,37 @@
         <v>245.675</v>
       </c>
       <c r="M94">
-        <v>703.8705456000001</v>
+        <v>711.5213124000002</v>
       </c>
       <c r="N94">
-        <v>-458.1955456000002</v>
+        <v>-465.8463124000002</v>
       </c>
       <c r="O94">
-        <v>-45.81955456000002</v>
+        <v>-46.58463124000002</v>
       </c>
       <c r="P94">
-        <v>-412.3759910400001</v>
+        <v>-419.2616811600002</v>
       </c>
       <c r="Q94">
-        <v>-303.1759910400002</v>
+        <v>-310.0616811600002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6263660598973738</v>
+        <v>0.7093040684541416</v>
       </c>
       <c r="T94">
-        <v>11.63666869890459</v>
+        <v>13.29904994160525</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03490343523191176</v>
+        <v>0.03452812947672991</v>
       </c>
       <c r="W94">
-        <v>0.2275697699723152</v>
+        <v>0.2276582670693871</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3490343523191176</v>
+        <v>0.3452812947672991</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2613734731663199</v>
+        <v>0.2632734731663199</v>
       </c>
       <c r="C95">
-        <v>-2103.107317968434</v>
+        <v>-2141.65127684384</v>
       </c>
       <c r="D95">
-        <v>697.9706820315662</v>
+        <v>691.8727231561602</v>
       </c>
       <c r="E95">
-        <v>1471.778</v>
+        <v>1504.224</v>
       </c>
       <c r="F95">
-        <v>3017.478000000001</v>
+        <v>3049.924</v>
       </c>
       <c r="G95">
         <v>216.4</v>
@@ -9071,37 +9071,37 @@
         <v>245.675</v>
       </c>
       <c r="M95">
-        <v>711.5213124000002</v>
+        <v>719.1720792000001</v>
       </c>
       <c r="N95">
-        <v>-465.8463124000002</v>
+        <v>-473.4970792000001</v>
       </c>
       <c r="O95">
-        <v>-46.58463124000002</v>
+        <v>-47.34970792000001</v>
       </c>
       <c r="P95">
-        <v>-419.2616811600002</v>
+        <v>-426.1473712800001</v>
       </c>
       <c r="Q95">
-        <v>-310.0616811600002</v>
+        <v>-316.9473712800001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7093040684541416</v>
+        <v>0.8198880798631653</v>
       </c>
       <c r="T95">
-        <v>13.29904994160525</v>
+        <v>15.51555826520613</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03452812947672991</v>
+        <v>0.03416080895038173</v>
       </c>
       <c r="W95">
-        <v>0.2276582670693871</v>
+        <v>0.2277448812495</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3452812947672991</v>
+        <v>0.3416080895038172</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2632734731663199</v>
+        <v>0.2651734731663199</v>
       </c>
       <c r="C96">
-        <v>-2141.65127684384</v>
+        <v>-2180.089606522643</v>
       </c>
       <c r="D96">
-        <v>691.8727231561602</v>
+        <v>685.8803934773567</v>
       </c>
       <c r="E96">
-        <v>1504.224</v>
+        <v>1536.67</v>
       </c>
       <c r="F96">
-        <v>3049.924</v>
+        <v>3082.37</v>
       </c>
       <c r="G96">
         <v>216.4</v>
@@ -9153,37 +9153,37 @@
         <v>245.675</v>
       </c>
       <c r="M96">
-        <v>719.1720792000001</v>
+        <v>726.8228460000001</v>
       </c>
       <c r="N96">
-        <v>-473.4970792000001</v>
+        <v>-481.1478460000002</v>
       </c>
       <c r="O96">
-        <v>-47.34970792000001</v>
+        <v>-48.11478460000002</v>
       </c>
       <c r="P96">
-        <v>-426.1473712800001</v>
+        <v>-433.0330614000002</v>
       </c>
       <c r="Q96">
-        <v>-316.9473712800001</v>
+        <v>-323.8330614000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8198880798631653</v>
+        <v>0.974705695835799</v>
       </c>
       <c r="T96">
-        <v>15.51555826520613</v>
+        <v>18.61866991824736</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03416080895038173</v>
+        <v>0.03380122148774613</v>
       </c>
       <c r="W96">
-        <v>0.2277448812495</v>
+        <v>0.2278296719731895</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3416080895038172</v>
+        <v>0.3380122148774612</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2651734731663199</v>
+        <v>0.2670734731663199</v>
       </c>
       <c r="C97">
-        <v>-2180.089606522643</v>
+        <v>-2218.42502801072</v>
       </c>
       <c r="D97">
-        <v>685.8803934773567</v>
+        <v>679.9909719892805</v>
       </c>
       <c r="E97">
-        <v>1536.67</v>
+        <v>1569.116000000001</v>
       </c>
       <c r="F97">
-        <v>3082.37</v>
+        <v>3114.816000000001</v>
       </c>
       <c r="G97">
         <v>216.4</v>
@@ -9235,37 +9235,37 @@
         <v>245.675</v>
       </c>
       <c r="M97">
-        <v>726.8228460000001</v>
+        <v>734.4736128000002</v>
       </c>
       <c r="N97">
-        <v>-481.1478460000002</v>
+        <v>-488.7986128000002</v>
       </c>
       <c r="O97">
-        <v>-48.11478460000002</v>
+        <v>-48.87986128000003</v>
       </c>
       <c r="P97">
-        <v>-433.0330614000002</v>
+        <v>-439.9187515200002</v>
       </c>
       <c r="Q97">
-        <v>-323.8330614000002</v>
+        <v>-330.7187515200002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.974705695835799</v>
+        <v>1.206932119794749</v>
       </c>
       <c r="T97">
-        <v>18.61866991824736</v>
+        <v>23.27333739780921</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03380122148774613</v>
+        <v>0.0334491254305821</v>
       </c>
       <c r="W97">
-        <v>0.2278296719731895</v>
+        <v>0.2279126962234687</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3380122148774612</v>
+        <v>0.3344912543058209</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2670734731663199</v>
+        <v>0.2689734731663199</v>
       </c>
       <c r="C98">
-        <v>-2218.42502801072</v>
+        <v>-2256.660169652194</v>
       </c>
       <c r="D98">
-        <v>679.9909719892805</v>
+        <v>674.2018303478061</v>
       </c>
       <c r="E98">
-        <v>1569.116</v>
+        <v>1601.562</v>
       </c>
       <c r="F98">
-        <v>3114.816</v>
+        <v>3147.262</v>
       </c>
       <c r="G98">
         <v>216.4</v>
@@ -9317,37 +9317,37 @@
         <v>245.675</v>
       </c>
       <c r="M98">
-        <v>734.4736128000001</v>
+        <v>742.1243796000001</v>
       </c>
       <c r="N98">
-        <v>-488.7986128000001</v>
+        <v>-496.4493796000002</v>
       </c>
       <c r="O98">
-        <v>-48.87986128000001</v>
+        <v>-49.64493796000002</v>
       </c>
       <c r="P98">
-        <v>-439.9187515200001</v>
+        <v>-446.8044416400002</v>
       </c>
       <c r="Q98">
-        <v>-330.7187515200001</v>
+        <v>-337.6044416400002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.206932119794746</v>
+        <v>1.593976159726328</v>
       </c>
       <c r="T98">
-        <v>23.27333739780915</v>
+        <v>31.03111653041221</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03344912543058211</v>
+        <v>0.03310428908593693</v>
       </c>
       <c r="W98">
-        <v>0.2279126962234687</v>
+        <v>0.2279940086335361</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3344912543058211</v>
+        <v>0.3310428908593692</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2689734731663199</v>
+        <v>0.2708734731663199</v>
       </c>
       <c r="C99">
-        <v>-2256.660169652194</v>
+        <v>-2294.79757104055</v>
       </c>
       <c r="D99">
-        <v>674.2018303478061</v>
+        <v>668.5104289594505</v>
       </c>
       <c r="E99">
-        <v>1601.562</v>
+        <v>1634.008</v>
       </c>
       <c r="F99">
-        <v>3147.262</v>
+        <v>3179.708</v>
       </c>
       <c r="G99">
         <v>216.4</v>
@@ -9399,37 +9399,37 @@
         <v>245.675</v>
       </c>
       <c r="M99">
-        <v>742.1243796000001</v>
+        <v>749.7751464</v>
       </c>
       <c r="N99">
-        <v>-496.4493796000002</v>
+        <v>-504.1001464000001</v>
       </c>
       <c r="O99">
-        <v>-49.64493796000002</v>
+        <v>-50.41001464000001</v>
       </c>
       <c r="P99">
-        <v>-446.8044416400002</v>
+        <v>-453.6901317600001</v>
       </c>
       <c r="Q99">
-        <v>-337.6044416400002</v>
+        <v>-344.4901317600001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.593976159726328</v>
+        <v>2.368064239589492</v>
       </c>
       <c r="T99">
-        <v>31.03111653041221</v>
+        <v>46.5466747956183</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03310428908593693</v>
+        <v>0.03276649021771309</v>
       </c>
       <c r="W99">
-        <v>0.2279940086335361</v>
+        <v>0.2280736616066633</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3310428908593692</v>
+        <v>0.3276649021771308</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2708734731663199</v>
+        <v>0.2727734731663199</v>
       </c>
       <c r="C100">
-        <v>-2294.79757104055</v>
+        <v>-2332.839686733295</v>
       </c>
       <c r="D100">
-        <v>668.5104289594505</v>
+        <v>662.914313266705</v>
       </c>
       <c r="E100">
-        <v>1634.008</v>
+        <v>1666.454</v>
       </c>
       <c r="F100">
-        <v>3179.708</v>
+        <v>3212.154</v>
       </c>
       <c r="G100">
         <v>216.4</v>
@@ -9481,37 +9481,37 @@
         <v>245.675</v>
       </c>
       <c r="M100">
-        <v>749.7751464</v>
+        <v>757.4259132000001</v>
       </c>
       <c r="N100">
-        <v>-504.1001464000001</v>
+        <v>-511.7509132000001</v>
       </c>
       <c r="O100">
-        <v>-50.41001464000001</v>
+        <v>-51.17509132000001</v>
       </c>
       <c r="P100">
-        <v>-453.6901317600001</v>
+        <v>-460.5758218800001</v>
       </c>
       <c r="Q100">
-        <v>-344.4901317600001</v>
+        <v>-351.3758218800001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.368064239589492</v>
+        <v>4.690328479178984</v>
       </c>
       <c r="T100">
-        <v>46.5466747956183</v>
+        <v>93.09334959123659</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03276649021771309</v>
+        <v>0.03243551556904931</v>
       </c>
       <c r="W100">
-        <v>0.2280736616066633</v>
+        <v>0.2281517054288182</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3276649021771308</v>
+        <v>0.3243551556904931</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2727734731663199</v>
-      </c>
-      <c r="C101">
-        <v>-2332.839686733295</v>
-      </c>
-      <c r="D101">
-        <v>662.914313266705</v>
-      </c>
-      <c r="E101">
-        <v>1666.454</v>
-      </c>
-      <c r="F101">
-        <v>3212.154</v>
-      </c>
-      <c r="G101">
-        <v>216.4</v>
-      </c>
-      <c r="H101">
-        <v>1698.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>354.8749999999999</v>
-      </c>
-      <c r="K101">
-        <v>109.2</v>
-      </c>
-      <c r="L101">
-        <v>245.675</v>
-      </c>
-      <c r="M101">
-        <v>757.4259132000001</v>
-      </c>
-      <c r="N101">
-        <v>-511.7509132000001</v>
-      </c>
-      <c r="O101">
-        <v>-51.17509132000001</v>
-      </c>
-      <c r="P101">
-        <v>-460.5758218800001</v>
-      </c>
-      <c r="Q101">
-        <v>-351.3758218800001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.690328479178984</v>
-      </c>
-      <c r="T101">
-        <v>93.09334959123659</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03243551556904931</v>
-      </c>
-      <c r="W101">
-        <v>0.2281517054288182</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3243551556904931</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
